--- a/docs/bls-data/World-Campus-BLS-Data-Latest.xlsx
+++ b/docs/bls-data/World-Campus-BLS-Data-Latest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jci2\Documents\GitHub\bls-data-conversion\docs\bls-data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jci2\Documents\World Campus\Program Page Redesign\BLS Data\For Prog Page\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3651314-DD01-4E58-8608-E9BE6DE60E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB945C40-3C9C-4863-9840-0BFF9BEB9F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A3512B26-53A5-4F1E-B37D-F8DA2B75D3A8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A3512B26-53A5-4F1E-B37D-F8DA2B75D3A8}"/>
   </bookViews>
   <sheets>
     <sheet name="Employment" sheetId="5" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Employment!$A$1:$J$302</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Job Titles'!$A$1:$E$502</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Job Titles'!$A$1:$E$547</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4005" uniqueCount="903">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4005" uniqueCount="904">
   <si>
     <t>prospect_code</t>
   </si>
@@ -2245,15 +2245,6 @@
     <t>Nuclear Reactor Engineer</t>
   </si>
   <si>
-    <t>Emergency Department RN (Emergency Department Registered Nurse)</t>
-  </si>
-  <si>
-    <t>School Nurse</t>
-  </si>
-  <si>
-    <t>Staff RN (Staff Registered Nurse)</t>
-  </si>
-  <si>
     <t>Clinical Dietitian</t>
   </si>
   <si>
@@ -2750,6 +2741,18 @@
   </si>
   <si>
     <t>Revenue Tax Specialist</t>
+  </si>
+  <si>
+    <t>Nursing Supervisor</t>
+  </si>
+  <si>
+    <t>Charge Nurse </t>
+  </si>
+  <si>
+    <t>Nurse Coordinator </t>
+  </si>
+  <si>
+    <t>Staff Nurse Team Leader </t>
   </si>
 </sst>
 </file>
@@ -3667,14 +3670,14 @@
     </row>
     <row r="16" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="3" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>13</v>
@@ -3697,14 +3700,14 @@
     </row>
     <row r="17" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="3" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>13</v>
@@ -3727,14 +3730,14 @@
     </row>
     <row r="18" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="3" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>13</v>
@@ -4905,7 +4908,7 @@
     </row>
     <row r="55" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>11</v>
@@ -4914,7 +4917,7 @@
         <v>2539</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>13</v>
@@ -4937,7 +4940,7 @@
     </row>
     <row r="56" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>11</v>
@@ -4946,7 +4949,7 @@
         <v>2539</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>13</v>
@@ -4969,7 +4972,7 @@
     </row>
     <row r="57" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>11</v>
@@ -4978,7 +4981,7 @@
         <v>2539</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>13</v>
@@ -6135,14 +6138,14 @@
     </row>
     <row r="94" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" s="3" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>13</v>
@@ -6165,14 +6168,14 @@
     </row>
     <row r="95" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" s="3" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>13</v>
@@ -6195,14 +6198,14 @@
     </row>
     <row r="96" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" s="3" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>13</v>
@@ -6225,14 +6228,14 @@
     </row>
     <row r="97" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" s="3" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>13</v>
@@ -6255,14 +6258,14 @@
     </row>
     <row r="98" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" s="3" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>13</v>
@@ -6285,14 +6288,14 @@
     </row>
     <row r="99" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" s="3" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>13</v>
@@ -7755,14 +7758,14 @@
     </row>
     <row r="145" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" s="3" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="E145" s="3" t="s">
         <v>13</v>
@@ -7785,14 +7788,14 @@
     </row>
     <row r="146" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" s="3" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="E146" s="3" t="s">
         <v>13</v>
@@ -7815,14 +7818,14 @@
     </row>
     <row r="147" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" s="3" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="E147" s="3" t="s">
         <v>13</v>
@@ -9061,14 +9064,14 @@
     </row>
     <row r="186" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="B186" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" s="3" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="E186" s="3" t="s">
         <v>13</v>
@@ -9091,14 +9094,14 @@
     </row>
     <row r="187" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" s="3" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="E187" s="3" t="s">
         <v>13</v>
@@ -9121,14 +9124,14 @@
     </row>
     <row r="188" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="B188" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" s="3" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="E188" s="3" t="s">
         <v>13</v>
@@ -9151,14 +9154,14 @@
     </row>
     <row r="189" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="B189" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" s="3" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="E189" s="3" t="s">
         <v>13</v>
@@ -9181,14 +9184,14 @@
     </row>
     <row r="190" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="B190" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" s="3" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="E190" s="3" t="s">
         <v>13</v>
@@ -9211,14 +9214,14 @@
     </row>
     <row r="191" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="B191" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" s="3" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="E191" s="3" t="s">
         <v>13</v>
@@ -9241,14 +9244,14 @@
     </row>
     <row r="192" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" s="3" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="E192" s="3" t="s">
         <v>13</v>
@@ -9271,14 +9274,14 @@
     </row>
     <row r="193" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="3" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="B193" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" s="3" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="E193" s="3" t="s">
         <v>13</v>
@@ -9304,7 +9307,7 @@
         <v>458</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" s="3" t="s">
@@ -9334,7 +9337,7 @@
         <v>458</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" s="3" t="s">
@@ -9364,7 +9367,7 @@
         <v>458</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" s="3" t="s">
@@ -9394,7 +9397,7 @@
         <v>458</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" s="3" t="s">
@@ -9424,7 +9427,7 @@
         <v>458</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" s="3" t="s">
@@ -11147,7 +11150,7 @@
     </row>
     <row r="252" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="3" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="B252" s="3" t="s">
         <v>11</v>
@@ -11156,7 +11159,7 @@
         <v>2542</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="E252" s="3" t="s">
         <v>13</v>
@@ -11186,7 +11189,7 @@
       </c>
       <c r="C253" s="2"/>
       <c r="D253" s="3" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="E253" s="3" t="s">
         <v>13</v>
@@ -11401,14 +11404,14 @@
     </row>
     <row r="260" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="3" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="B260" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" s="3" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="E260" s="3" t="s">
         <v>13</v>
@@ -11431,23 +11434,23 @@
     </row>
     <row r="261" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="3" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="B261" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" s="3" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="E261" s="3" t="s">
         <v>13</v>
       </c>
       <c r="F261" s="3" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="G261" s="3" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="H261" s="5">
         <v>33340</v>
@@ -11461,14 +11464,14 @@
     </row>
     <row r="262" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="3" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="B262" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" s="3" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="E262" s="3" t="s">
         <v>13</v>
@@ -11491,23 +11494,23 @@
     </row>
     <row r="263" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="3" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="B263" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="E263" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F263" s="3" t="s">
         <v>866</v>
       </c>
-      <c r="E263" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F263" s="3" t="s">
-        <v>869</v>
-      </c>
       <c r="G263" s="3" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="H263" s="5">
         <v>185940</v>
@@ -11521,23 +11524,23 @@
     </row>
     <row r="264" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="3" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="B264" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" s="3" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="E264" s="3" t="s">
         <v>13</v>
       </c>
       <c r="F264" s="3" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="G264" s="3" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="H264" s="5">
         <v>125910</v>
@@ -11551,23 +11554,23 @@
     </row>
     <row r="265" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="3" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="B265" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" s="3" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="E265" s="3" t="s">
         <v>13</v>
       </c>
       <c r="F265" s="3" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="G265" s="3" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="H265" s="5">
         <v>64940</v>
@@ -12477,7 +12480,7 @@
     </row>
     <row r="294" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="B294" s="3" t="s">
         <v>11</v>
@@ -12507,7 +12510,7 @@
     </row>
     <row r="295" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="B295" s="3" t="s">
         <v>11</v>
@@ -13257,14 +13260,14 @@
     </row>
     <row r="29" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="7" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>523</v>
@@ -13272,14 +13275,14 @@
     </row>
     <row r="30" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="7" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>524</v>
@@ -13287,44 +13290,44 @@
     </row>
     <row r="31" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="7" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="7" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="7" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>496</v>
@@ -13332,14 +13335,14 @@
     </row>
     <row r="34" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="7" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>522</v>
@@ -14360,7 +14363,7 @@
         <v>463</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14375,7 +14378,7 @@
         <v>463</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14410,7 +14413,7 @@
     </row>
     <row r="98" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="B98" s="7" t="s">
         <v>11</v>
@@ -14419,7 +14422,7 @@
         <v>2539</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="E98" s="7" t="s">
         <v>564</v>
@@ -14427,7 +14430,7 @@
     </row>
     <row r="99" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="B99" s="7" t="s">
         <v>11</v>
@@ -14436,7 +14439,7 @@
         <v>2539</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="E99" s="7" t="s">
         <v>563</v>
@@ -14444,7 +14447,7 @@
     </row>
     <row r="100" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="B100" s="7" t="s">
         <v>11</v>
@@ -14453,7 +14456,7 @@
         <v>2539</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="E100" s="7" t="s">
         <v>566</v>
@@ -14461,7 +14464,7 @@
     </row>
     <row r="101" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>11</v>
@@ -14470,7 +14473,7 @@
         <v>2539</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="E101" s="7" t="s">
         <v>565</v>
@@ -14478,7 +14481,7 @@
     </row>
     <row r="102" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="B102" s="7" t="s">
         <v>11</v>
@@ -14487,10 +14490,10 @@
         <v>2539</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14505,7 +14508,7 @@
         <v>461</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14550,7 +14553,7 @@
         <v>461</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14971,7 +14974,7 @@
         <v>161</v>
       </c>
       <c r="E131" s="7" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14986,7 +14989,7 @@
         <v>161</v>
       </c>
       <c r="E132" s="7" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15001,7 +15004,7 @@
         <v>161</v>
       </c>
       <c r="E133" s="7" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15016,7 +15019,7 @@
         <v>161</v>
       </c>
       <c r="E134" s="7" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15561,29 +15564,29 @@
     </row>
     <row r="167" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C167" s="9"/>
       <c r="D167" s="7" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="E167" s="7" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="7" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="B168" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C168" s="9"/>
       <c r="D168" s="7" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="E168" s="7" t="s">
         <v>560</v>
@@ -15591,14 +15594,14 @@
     </row>
     <row r="169" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="B169" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C169" s="9"/>
       <c r="D169" s="7" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="E169" s="7" t="s">
         <v>580</v>
@@ -15606,14 +15609,14 @@
     </row>
     <row r="170" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="7" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="B170" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C170" s="9"/>
       <c r="D170" s="7" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="E170" s="7" t="s">
         <v>579</v>
@@ -15621,59 +15624,59 @@
     </row>
     <row r="171" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="B171" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C171" s="9"/>
       <c r="D171" s="7" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="E171" s="7" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="7" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="B172" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C172" s="9"/>
       <c r="D172" s="7" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="E172" s="7" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="7" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="B173" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C173" s="9"/>
       <c r="D173" s="7" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="E173" s="7" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="7" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="B174" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C174" s="9"/>
       <c r="D174" s="7" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="E174" s="7" t="s">
         <v>580</v>
@@ -15681,47 +15684,47 @@
     </row>
     <row r="175" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="B175" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C175" s="9"/>
       <c r="D175" s="7" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="E175" s="7" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="7" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="B176" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C176" s="9"/>
       <c r="D176" s="7" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="E176" s="7" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="B177" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C177" s="9"/>
       <c r="D177" s="7" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="E177" s="7" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
     </row>
     <row r="178" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15908,7 +15911,7 @@
         <v>205</v>
       </c>
       <c r="E188" s="7" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
     </row>
     <row r="189" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15925,7 +15928,7 @@
         <v>205</v>
       </c>
       <c r="E189" s="7" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
     </row>
     <row r="190" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15942,7 +15945,7 @@
         <v>205</v>
       </c>
       <c r="E190" s="7" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
     </row>
     <row r="191" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15976,7 +15979,7 @@
         <v>205</v>
       </c>
       <c r="E192" s="7" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
     </row>
     <row r="193" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15993,7 +15996,7 @@
         <v>205</v>
       </c>
       <c r="E193" s="7" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
     </row>
     <row r="194" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16027,7 +16030,7 @@
         <v>205</v>
       </c>
       <c r="E195" s="7" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
     </row>
     <row r="196" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -17154,29 +17157,29 @@
     </row>
     <row r="262" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="7" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="B262" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C262" s="9"/>
       <c r="D262" s="7" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="E262" s="7" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
     </row>
     <row r="263" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="7" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="B263" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C263" s="9"/>
       <c r="D263" s="7" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="E263" s="7" t="s">
         <v>658</v>
@@ -17184,62 +17187,62 @@
     </row>
     <row r="264" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="7" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="B264" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C264" s="9"/>
       <c r="D264" s="7" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="E264" s="7" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
     </row>
     <row r="265" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="7" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="B265" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C265" s="9"/>
       <c r="D265" s="7" t="s">
+        <v>883</v>
+      </c>
+      <c r="E265" s="7" t="s">
         <v>886</v>
-      </c>
-      <c r="E265" s="7" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="266" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="7" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C266" s="9"/>
       <c r="D266" s="7" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="E266" s="7" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
     </row>
     <row r="267" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="7" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="B267" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C267" s="9"/>
       <c r="D267" s="7" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="E267" s="7" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
     </row>
     <row r="268" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18315,59 +18318,59 @@
     </row>
     <row r="331" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="7" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="B331" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C331" s="9"/>
       <c r="D331" s="7" t="s">
+        <v>845</v>
+      </c>
+      <c r="E331" s="7" t="s">
         <v>848</v>
-      </c>
-      <c r="E331" s="7" t="s">
-        <v>851</v>
       </c>
     </row>
     <row r="332" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="7" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C332" s="9"/>
       <c r="D332" s="7" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="E332" s="7" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
     </row>
     <row r="333" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="7" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="B333" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C333" s="9"/>
       <c r="D333" s="7" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="E333" s="7" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
     </row>
     <row r="334" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="7" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="B334" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C334" s="9"/>
       <c r="D334" s="7" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="E334" s="7" t="s">
         <v>524</v>
@@ -18375,29 +18378,29 @@
     </row>
     <row r="335" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="7" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="B335" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C335" s="9"/>
       <c r="D335" s="7" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="E335" s="7" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
     </row>
     <row r="336" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="7" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="B336" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C336" s="9"/>
       <c r="D336" s="7" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="E336" s="7" t="s">
         <v>523</v>
@@ -18405,14 +18408,14 @@
     </row>
     <row r="337" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="7" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="B337" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C337" s="9"/>
       <c r="D337" s="7" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="E337" s="7" t="s">
         <v>562</v>
@@ -18420,14 +18423,14 @@
     </row>
     <row r="338" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="7" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="B338" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C338" s="9"/>
       <c r="D338" s="7" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="E338" s="7" t="s">
         <v>522</v>
@@ -18445,7 +18448,7 @@
         <v>459</v>
       </c>
       <c r="E339" s="7" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
     </row>
     <row r="340" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18475,7 +18478,7 @@
         <v>459</v>
       </c>
       <c r="E341" s="7" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
     </row>
     <row r="342" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18490,7 +18493,7 @@
         <v>459</v>
       </c>
       <c r="E342" s="7" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
     </row>
     <row r="343" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18520,7 +18523,7 @@
         <v>459</v>
       </c>
       <c r="E344" s="7" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
     </row>
     <row r="345" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18535,7 +18538,7 @@
         <v>459</v>
       </c>
       <c r="E345" s="7" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
     </row>
     <row r="346" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18550,7 +18553,7 @@
         <v>459</v>
       </c>
       <c r="E346" s="7" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
     </row>
     <row r="347" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18822,7 +18825,7 @@
         <v>343</v>
       </c>
       <c r="E362" s="7" t="s">
-        <v>736</v>
+        <v>900</v>
       </c>
     </row>
     <row r="363" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18839,7 +18842,7 @@
         <v>343</v>
       </c>
       <c r="E363" s="7" t="s">
-        <v>735</v>
+        <v>901</v>
       </c>
     </row>
     <row r="364" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18856,7 +18859,7 @@
         <v>343</v>
       </c>
       <c r="E364" s="7" t="s">
-        <v>695</v>
+        <v>902</v>
       </c>
     </row>
     <row r="365" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18873,7 +18876,7 @@
         <v>343</v>
       </c>
       <c r="E365" s="7" t="s">
-        <v>734</v>
+        <v>903</v>
       </c>
     </row>
     <row r="366" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19043,7 +19046,7 @@
         <v>351</v>
       </c>
       <c r="E375" s="7" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
     </row>
     <row r="376" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19060,7 +19063,7 @@
         <v>351</v>
       </c>
       <c r="E376" s="7" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
     </row>
     <row r="377" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19077,7 +19080,7 @@
         <v>351</v>
       </c>
       <c r="E377" s="7" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
     </row>
     <row r="378" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19094,7 +19097,7 @@
         <v>351</v>
       </c>
       <c r="E378" s="7" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
     </row>
     <row r="379" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19111,7 +19114,7 @@
         <v>351</v>
       </c>
       <c r="E379" s="7" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
     </row>
     <row r="380" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19213,7 +19216,7 @@
         <v>357</v>
       </c>
       <c r="E385" s="7" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
     </row>
     <row r="386" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19230,7 +19233,7 @@
         <v>357</v>
       </c>
       <c r="E386" s="7" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
     </row>
     <row r="387" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19247,7 +19250,7 @@
         <v>357</v>
       </c>
       <c r="E387" s="7" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
     </row>
     <row r="388" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19264,7 +19267,7 @@
         <v>357</v>
       </c>
       <c r="E388" s="7" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="389" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19281,7 +19284,7 @@
         <v>357</v>
       </c>
       <c r="E389" s="7" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
     </row>
     <row r="390" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19298,7 +19301,7 @@
         <v>357</v>
       </c>
       <c r="E390" s="7" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
     </row>
     <row r="391" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19315,7 +19318,7 @@
         <v>357</v>
       </c>
       <c r="E391" s="7" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
     </row>
     <row r="392" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19332,7 +19335,7 @@
         <v>357</v>
       </c>
       <c r="E392" s="7" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="393" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19349,7 +19352,7 @@
         <v>367</v>
       </c>
       <c r="E393" s="7" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="394" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19366,7 +19369,7 @@
         <v>367</v>
       </c>
       <c r="E394" s="7" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
     </row>
     <row r="395" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19383,7 +19386,7 @@
         <v>367</v>
       </c>
       <c r="E395" s="7" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="396" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19400,7 +19403,7 @@
         <v>367</v>
       </c>
       <c r="E396" s="7" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
     </row>
     <row r="397" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19417,7 +19420,7 @@
         <v>367</v>
       </c>
       <c r="E397" s="7" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
     </row>
     <row r="398" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19434,7 +19437,7 @@
         <v>367</v>
       </c>
       <c r="E398" s="7" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
     </row>
     <row r="399" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19451,7 +19454,7 @@
         <v>367</v>
       </c>
       <c r="E399" s="7" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
     </row>
     <row r="400" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19468,7 +19471,7 @@
         <v>367</v>
       </c>
       <c r="E400" s="7" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
     </row>
     <row r="401" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19485,7 +19488,7 @@
         <v>369</v>
       </c>
       <c r="E401" s="7" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
     </row>
     <row r="402" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19502,7 +19505,7 @@
         <v>369</v>
       </c>
       <c r="E402" s="7" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
     </row>
     <row r="403" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19536,7 +19539,7 @@
         <v>369</v>
       </c>
       <c r="E404" s="7" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
     </row>
     <row r="405" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19553,7 +19556,7 @@
         <v>369</v>
       </c>
       <c r="E405" s="7" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
     </row>
     <row r="406" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19570,7 +19573,7 @@
         <v>373</v>
       </c>
       <c r="E406" s="7" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
     </row>
     <row r="407" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19587,7 +19590,7 @@
         <v>373</v>
       </c>
       <c r="E407" s="7" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
     </row>
     <row r="408" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19604,7 +19607,7 @@
         <v>373</v>
       </c>
       <c r="E408" s="7" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
     </row>
     <row r="409" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19638,7 +19641,7 @@
         <v>373</v>
       </c>
       <c r="E410" s="7" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
     </row>
     <row r="411" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19655,7 +19658,7 @@
         <v>375</v>
       </c>
       <c r="E411" s="7" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
     </row>
     <row r="412" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19672,7 +19675,7 @@
         <v>375</v>
       </c>
       <c r="E412" s="7" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
     </row>
     <row r="413" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19689,7 +19692,7 @@
         <v>375</v>
       </c>
       <c r="E413" s="7" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
     </row>
     <row r="414" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19706,7 +19709,7 @@
         <v>375</v>
       </c>
       <c r="E414" s="7" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
     </row>
     <row r="415" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19723,7 +19726,7 @@
         <v>375</v>
       </c>
       <c r="E415" s="7" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
     </row>
     <row r="416" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19740,7 +19743,7 @@
         <v>381</v>
       </c>
       <c r="E416" s="7" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
     </row>
     <row r="417" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19757,7 +19760,7 @@
         <v>381</v>
       </c>
       <c r="E417" s="7" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
     </row>
     <row r="418" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19774,7 +19777,7 @@
         <v>381</v>
       </c>
       <c r="E418" s="7" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
     </row>
     <row r="419" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19791,7 +19794,7 @@
         <v>381</v>
       </c>
       <c r="E419" s="7" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
     </row>
     <row r="420" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19808,7 +19811,7 @@
         <v>381</v>
       </c>
       <c r="E420" s="7" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
     </row>
     <row r="421" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19825,7 +19828,7 @@
         <v>383</v>
       </c>
       <c r="E421" s="7" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
     </row>
     <row r="422" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19842,7 +19845,7 @@
         <v>383</v>
       </c>
       <c r="E422" s="7" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
     </row>
     <row r="423" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19859,7 +19862,7 @@
         <v>383</v>
       </c>
       <c r="E423" s="7" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
     </row>
     <row r="424" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19876,7 +19879,7 @@
         <v>383</v>
       </c>
       <c r="E424" s="7" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
     </row>
     <row r="425" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19893,7 +19896,7 @@
         <v>383</v>
       </c>
       <c r="E425" s="7" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
     </row>
     <row r="426" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19927,7 +19930,7 @@
         <v>389</v>
       </c>
       <c r="E427" s="7" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
     </row>
     <row r="428" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19944,7 +19947,7 @@
         <v>389</v>
       </c>
       <c r="E428" s="7" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
     </row>
     <row r="429" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19961,7 +19964,7 @@
         <v>389</v>
       </c>
       <c r="E429" s="7" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
     </row>
     <row r="430" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19978,7 +19981,7 @@
         <v>389</v>
       </c>
       <c r="E430" s="7" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
     </row>
     <row r="431" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19995,7 +19998,7 @@
         <v>391</v>
       </c>
       <c r="E431" s="7" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="432" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20012,7 +20015,7 @@
         <v>391</v>
       </c>
       <c r="E432" s="7" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
     </row>
     <row r="433" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20029,7 +20032,7 @@
         <v>391</v>
       </c>
       <c r="E433" s="7" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
     </row>
     <row r="434" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20046,7 +20049,7 @@
         <v>391</v>
       </c>
       <c r="E434" s="7" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
     </row>
     <row r="435" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20097,7 +20100,7 @@
         <v>395</v>
       </c>
       <c r="E437" s="7" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
     </row>
     <row r="438" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20114,7 +20117,7 @@
         <v>395</v>
       </c>
       <c r="E438" s="7" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
     </row>
     <row r="439" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20131,7 +20134,7 @@
         <v>395</v>
       </c>
       <c r="E439" s="7" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
     </row>
     <row r="440" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20148,7 +20151,7 @@
         <v>395</v>
       </c>
       <c r="E440" s="7" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="441" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20165,7 +20168,7 @@
         <v>397</v>
       </c>
       <c r="E441" s="7" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
     </row>
     <row r="442" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20216,7 +20219,7 @@
         <v>397</v>
       </c>
       <c r="E444" s="7" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
     </row>
     <row r="445" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20233,7 +20236,7 @@
         <v>397</v>
       </c>
       <c r="E445" s="7" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
     </row>
     <row r="446" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20267,7 +20270,7 @@
         <v>401</v>
       </c>
       <c r="E447" s="7" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
     </row>
     <row r="448" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20284,7 +20287,7 @@
         <v>401</v>
       </c>
       <c r="E448" s="7" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
     </row>
     <row r="449" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20301,7 +20304,7 @@
         <v>401</v>
       </c>
       <c r="E449" s="7" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
     </row>
     <row r="450" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20335,7 +20338,7 @@
         <v>401</v>
       </c>
       <c r="E451" s="7" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
     </row>
     <row r="452" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20349,10 +20352,10 @@
         <v>2542</v>
       </c>
       <c r="D452" s="7" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="E452" s="7" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
     </row>
     <row r="453" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20366,10 +20369,10 @@
         <v>2542</v>
       </c>
       <c r="D453" s="7" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="E453" s="7" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
     </row>
     <row r="454" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20383,10 +20386,10 @@
         <v>2542</v>
       </c>
       <c r="D454" s="7" t="s">
+        <v>774</v>
+      </c>
+      <c r="E454" s="7" t="s">
         <v>777</v>
-      </c>
-      <c r="E454" s="7" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="455" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20400,10 +20403,10 @@
         <v>2542</v>
       </c>
       <c r="D455" s="7" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="E455" s="7" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
     </row>
     <row r="456" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20417,10 +20420,10 @@
         <v>2542</v>
       </c>
       <c r="D456" s="7" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="E456" s="7" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
     </row>
     <row r="457" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20437,7 +20440,7 @@
         <v>406</v>
       </c>
       <c r="E457" s="7" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
     </row>
     <row r="458" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20454,7 +20457,7 @@
         <v>406</v>
       </c>
       <c r="E458" s="7" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
     </row>
     <row r="459" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20471,7 +20474,7 @@
         <v>406</v>
       </c>
       <c r="E459" s="7" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
     </row>
     <row r="460" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20505,7 +20508,7 @@
         <v>406</v>
       </c>
       <c r="E461" s="7" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
     </row>
     <row r="462" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20573,7 +20576,7 @@
         <v>408</v>
       </c>
       <c r="E465" s="7" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
     </row>
     <row r="466" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20607,49 +20610,49 @@
         <v>408</v>
       </c>
       <c r="E467" s="7" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
     </row>
     <row r="468" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="7" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="B468" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C468" s="9"/>
       <c r="D468" s="7" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="E468" s="7" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
     </row>
     <row r="469" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="7" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="B469" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C469" s="9"/>
       <c r="D469" s="7" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="E469" s="7" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
     </row>
     <row r="470" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="7" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="B470" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C470" s="9"/>
       <c r="D470" s="7" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="E470" s="7" t="s">
         <v>706</v>
@@ -20657,77 +20660,77 @@
     </row>
     <row r="471" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="7" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="B471" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C471" s="9"/>
       <c r="D471" s="7" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="E471" s="7" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
     </row>
     <row r="472" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="7" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="B472" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C472" s="9"/>
       <c r="D472" s="7" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="E472" s="7" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
     </row>
     <row r="473" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="7" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="B473" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C473" s="9"/>
       <c r="D473" s="7" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="E473" s="7" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
     </row>
     <row r="474" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="7" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="B474" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C474" s="9"/>
       <c r="D474" s="7" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="E474" s="7" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
     </row>
     <row r="475" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="7" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C475" s="9"/>
       <c r="D475" s="7" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="E475" s="7" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
     </row>
     <row r="476" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20761,7 +20764,7 @@
         <v>410</v>
       </c>
       <c r="E477" s="7" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
     </row>
     <row r="478" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20795,7 +20798,7 @@
         <v>410</v>
       </c>
       <c r="E479" s="7" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
     </row>
     <row r="480" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20812,7 +20815,7 @@
         <v>410</v>
       </c>
       <c r="E480" s="7" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
     </row>
     <row r="481" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20846,7 +20849,7 @@
         <v>414</v>
       </c>
       <c r="E482" s="7" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
     </row>
     <row r="483" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20863,7 +20866,7 @@
         <v>414</v>
       </c>
       <c r="E483" s="7" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
     </row>
     <row r="484" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20880,7 +20883,7 @@
         <v>414</v>
       </c>
       <c r="E484" s="7" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
     </row>
     <row r="485" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20931,7 +20934,7 @@
         <v>416</v>
       </c>
       <c r="E487" s="7" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
     </row>
     <row r="488" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20948,7 +20951,7 @@
         <v>416</v>
       </c>
       <c r="E488" s="7" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
     </row>
     <row r="489" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20965,7 +20968,7 @@
         <v>416</v>
       </c>
       <c r="E489" s="7" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
     </row>
     <row r="490" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20982,7 +20985,7 @@
         <v>416</v>
       </c>
       <c r="E490" s="7" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="491" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20999,7 +21002,7 @@
         <v>418</v>
       </c>
       <c r="E491" s="7" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
     </row>
     <row r="492" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21016,7 +21019,7 @@
         <v>418</v>
       </c>
       <c r="E492" s="7" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
     </row>
     <row r="493" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21033,7 +21036,7 @@
         <v>418</v>
       </c>
       <c r="E493" s="7" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="494" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21050,7 +21053,7 @@
         <v>418</v>
       </c>
       <c r="E494" s="7" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
     </row>
     <row r="495" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21067,7 +21070,7 @@
         <v>418</v>
       </c>
       <c r="E495" s="7" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
     </row>
     <row r="496" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21084,7 +21087,7 @@
         <v>428</v>
       </c>
       <c r="E496" s="7" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
     </row>
     <row r="497" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21101,7 +21104,7 @@
         <v>428</v>
       </c>
       <c r="E497" s="7" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
     </row>
     <row r="498" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21118,7 +21121,7 @@
         <v>428</v>
       </c>
       <c r="E498" s="7" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
     </row>
     <row r="499" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21135,7 +21138,7 @@
         <v>428</v>
       </c>
       <c r="E499" s="7" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
     </row>
     <row r="500" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21152,7 +21155,7 @@
         <v>428</v>
       </c>
       <c r="E500" s="7" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
     </row>
     <row r="501" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21169,7 +21172,7 @@
         <v>428</v>
       </c>
       <c r="E501" s="7" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
     </row>
     <row r="502" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21186,7 +21189,7 @@
         <v>430</v>
       </c>
       <c r="E502" s="7" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
     </row>
     <row r="503" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21203,7 +21206,7 @@
         <v>430</v>
       </c>
       <c r="E503" s="7" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
     </row>
     <row r="504" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21220,7 +21223,7 @@
         <v>430</v>
       </c>
       <c r="E504" s="7" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
     </row>
     <row r="505" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21237,7 +21240,7 @@
         <v>430</v>
       </c>
       <c r="E505" s="7" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
     </row>
     <row r="506" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21254,7 +21257,7 @@
         <v>430</v>
       </c>
       <c r="E506" s="7" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
     </row>
     <row r="507" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21288,7 +21291,7 @@
         <v>432</v>
       </c>
       <c r="E508" s="7" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
     </row>
     <row r="509" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21339,7 +21342,7 @@
         <v>432</v>
       </c>
       <c r="E511" s="7" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
     </row>
     <row r="512" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21356,7 +21359,7 @@
         <v>434</v>
       </c>
       <c r="E512" s="7" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
     </row>
     <row r="513" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21373,7 +21376,7 @@
         <v>434</v>
       </c>
       <c r="E513" s="7" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
     </row>
     <row r="514" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21390,7 +21393,7 @@
         <v>434</v>
       </c>
       <c r="E514" s="7" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
     </row>
     <row r="515" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21407,7 +21410,7 @@
         <v>434</v>
       </c>
       <c r="E515" s="7" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
     </row>
     <row r="516" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21424,7 +21427,7 @@
         <v>434</v>
       </c>
       <c r="E516" s="7" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
     </row>
     <row r="517" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21441,7 +21444,7 @@
         <v>436</v>
       </c>
       <c r="E517" s="7" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
     </row>
     <row r="518" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21492,7 +21495,7 @@
         <v>436</v>
       </c>
       <c r="E520" s="7" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
     </row>
     <row r="521" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21509,7 +21512,7 @@
         <v>436</v>
       </c>
       <c r="E521" s="7" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
     </row>
     <row r="522" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21526,7 +21529,7 @@
         <v>436</v>
       </c>
       <c r="E522" s="7" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
     </row>
     <row r="523" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21560,7 +21563,7 @@
         <v>436</v>
       </c>
       <c r="E524" s="7" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
     </row>
     <row r="525" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21577,7 +21580,7 @@
         <v>436</v>
       </c>
       <c r="E525" s="7" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
     </row>
     <row r="526" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21594,12 +21597,12 @@
         <v>436</v>
       </c>
       <c r="E526" s="7" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
     </row>
     <row r="527" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="7" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="B527" s="7" t="s">
         <v>11</v>
@@ -21616,7 +21619,7 @@
     </row>
     <row r="528" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="7" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="B528" s="7" t="s">
         <v>11</v>
@@ -21633,7 +21636,7 @@
     </row>
     <row r="529" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="7" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="B529" s="7" t="s">
         <v>11</v>
@@ -21645,12 +21648,12 @@
         <v>437</v>
       </c>
       <c r="E529" s="7" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
     </row>
     <row r="530" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="7" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>11</v>
@@ -21662,12 +21665,12 @@
         <v>437</v>
       </c>
       <c r="E530" s="7" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
     </row>
     <row r="531" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="7" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="B531" s="7" t="s">
         <v>11</v>
@@ -21679,7 +21682,7 @@
         <v>437</v>
       </c>
       <c r="E531" s="7" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
     </row>
     <row r="532" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21781,7 +21784,7 @@
         <v>449</v>
       </c>
       <c r="E537" s="7" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
     </row>
     <row r="538" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21832,7 +21835,7 @@
         <v>449</v>
       </c>
       <c r="E540" s="7" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
     </row>
     <row r="541" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -21849,7 +21852,7 @@
         <v>449</v>
       </c>
       <c r="E541" s="7" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
     </row>
     <row r="542" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">

--- a/docs/bls-data/World-Campus-BLS-Data-Latest.xlsx
+++ b/docs/bls-data/World-Campus-BLS-Data-Latest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jci2\Documents\World Campus\Program Page Redesign\BLS Data\For Prog Page\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jci2\Documents\GitHub\bls-data-conversion\docs\bls-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1BFD2F9-1645-4E83-8A5B-069BA9CE1F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E36A3D5-3D39-4D79-84BA-13B672335F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A3512B26-53A5-4F1E-B37D-F8DA2B75D3A8}"/>
   </bookViews>
@@ -2804,6 +2804,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2934,7 +2937,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2978,34 +2981,27 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="17" fontId="6" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="6" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3017,6 +3013,18 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3403,7 +3411,7 @@
       <c r="H2" s="9">
         <v>1449500</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="31">
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="J2" s="8">
@@ -3435,7 +3443,7 @@
       <c r="H3" s="9">
         <v>47160</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3" s="31">
         <v>0.01</v>
       </c>
       <c r="J3" s="8">
@@ -3467,7 +3475,7 @@
       <c r="H4" s="9">
         <v>64390</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="31">
         <v>-4.3999999999999997E-2</v>
       </c>
       <c r="J4" s="8">
@@ -3499,7 +3507,7 @@
       <c r="H5" s="9">
         <v>1449500</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="31">
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="J5" s="8">
@@ -3531,7 +3539,7 @@
       <c r="H6" s="9">
         <v>67830</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="31">
         <v>0.185</v>
       </c>
       <c r="J6" s="8">
@@ -3563,7 +3571,7 @@
       <c r="H7" s="9">
         <v>47160</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="31">
         <v>0.01</v>
       </c>
       <c r="J7" s="8">
@@ -3595,7 +3603,7 @@
       <c r="H8" s="9">
         <v>154070</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="31">
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="J8" s="8">
@@ -3627,7 +3635,7 @@
       <c r="H9" s="9">
         <v>365740</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="31">
         <v>0.11</v>
       </c>
       <c r="J9" s="8">
@@ -3659,7 +3667,7 @@
       <c r="H10" s="9">
         <v>154070</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="31">
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="J10" s="8">
@@ -3691,7 +3699,7 @@
       <c r="H11" s="9">
         <v>27960</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="31">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="J11" s="8">
@@ -3723,7 +3731,7 @@
       <c r="H12" s="9">
         <v>6500</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="31">
         <v>-1.2999999999999999E-2</v>
       </c>
       <c r="J12" s="8">
@@ -3755,7 +3763,7 @@
       <c r="H13" s="9">
         <v>8220</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="31">
         <v>-2.5000000000000001E-2</v>
       </c>
       <c r="J13" s="8">
@@ -3787,7 +3795,7 @@
       <c r="H14" s="9">
         <v>262440</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="31">
         <v>0.33500000000000002</v>
       </c>
       <c r="J14" s="8">
@@ -3819,7 +3827,7 @@
       <c r="H15" s="9">
         <v>29030</v>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="31">
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="J15" s="8">
@@ -3849,7 +3857,7 @@
       <c r="H16" s="9">
         <v>1687890</v>
       </c>
-      <c r="I16" s="8">
+      <c r="I16" s="31">
         <v>0.158</v>
       </c>
       <c r="J16" s="8">
@@ -3879,7 +3887,7 @@
       <c r="H17" s="9">
         <v>262440</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="31">
         <v>0.33500000000000002</v>
       </c>
       <c r="J17" s="8">
@@ -3909,7 +3917,7 @@
       <c r="H18" s="9">
         <v>92230</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="31">
         <v>-0.06</v>
       </c>
       <c r="J18" s="8">
@@ -3941,7 +3949,7 @@
       <c r="H19" s="9">
         <v>61660</v>
       </c>
-      <c r="I19" s="8">
+      <c r="I19" s="31">
         <v>0.113</v>
       </c>
       <c r="J19" s="8">
@@ -3973,7 +3981,7 @@
       <c r="H20" s="9">
         <v>65690</v>
       </c>
-      <c r="I20" s="8">
+      <c r="I20" s="31">
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="J20" s="8">
@@ -4005,7 +4013,7 @@
       <c r="H21" s="9">
         <v>3503020</v>
       </c>
-      <c r="I21" s="8">
+      <c r="I21" s="31">
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="J21" s="8">
@@ -4037,7 +4045,7 @@
       <c r="H22" s="9">
         <v>263960</v>
       </c>
-      <c r="I22" s="8">
+      <c r="I22" s="31">
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="J22" s="8">
@@ -4069,7 +4077,7 @@
       <c r="H23" s="9">
         <v>3503020</v>
       </c>
-      <c r="I23" s="8">
+      <c r="I23" s="31">
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="J23" s="8">
@@ -4101,7 +4109,7 @@
       <c r="H24" s="9">
         <v>898280</v>
       </c>
-      <c r="I24" s="8">
+      <c r="I24" s="31">
         <v>8.7999999999999995E-2</v>
       </c>
       <c r="J24" s="8">
@@ -4133,7 +4141,7 @@
       <c r="H25" s="9">
         <v>204350</v>
       </c>
-      <c r="I25" s="8">
+      <c r="I25" s="31">
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="J25" s="8">
@@ -4165,7 +4173,7 @@
       <c r="H26" s="9">
         <v>3503020</v>
       </c>
-      <c r="I26" s="8">
+      <c r="I26" s="31">
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="J26" s="8">
@@ -4197,7 +4205,7 @@
       <c r="H27" s="9">
         <v>637080</v>
       </c>
-      <c r="I27" s="8">
+      <c r="I27" s="31">
         <v>4.7E-2</v>
       </c>
       <c r="J27" s="8">
@@ -4229,7 +4237,7 @@
       <c r="H28" s="9">
         <v>221180</v>
       </c>
-      <c r="I28" s="8">
+      <c r="I28" s="31">
         <v>6.0999999999999999E-2</v>
       </c>
       <c r="J28" s="8">
@@ -4261,7 +4269,7 @@
       <c r="H29" s="9">
         <v>246250</v>
       </c>
-      <c r="I29" s="8">
+      <c r="I29" s="31">
         <v>1.9E-2</v>
       </c>
       <c r="J29" s="8">
@@ -4269,88 +4277,88 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
+      <c r="A30" s="18" t="s">
         <v>907</v>
       </c>
-      <c r="B30" s="21"/>
+      <c r="B30" s="20"/>
       <c r="C30" s="17"/>
-      <c r="D30" s="21" t="s">
+      <c r="D30" s="20" t="s">
         <v>908</v>
       </c>
-      <c r="E30" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" s="23" t="s">
+      <c r="E30" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" s="21" t="s">
         <v>910</v>
       </c>
-      <c r="G30" s="26" t="s">
+      <c r="G30" s="24" t="s">
         <v>911</v>
       </c>
-      <c r="H30" s="27">
+      <c r="H30" s="25">
         <v>367840</v>
       </c>
-      <c r="I30" s="29">
+      <c r="I30" s="32">
         <v>0.05</v>
       </c>
-      <c r="J30" s="21">
+      <c r="J30" s="20">
         <f>I30*H30</f>
         <v>18392</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
+      <c r="A31" s="18" t="s">
         <v>907</v>
       </c>
-      <c r="B31" s="21"/>
+      <c r="B31" s="20"/>
       <c r="C31" s="17"/>
-      <c r="D31" s="21" t="s">
+      <c r="D31" s="20" t="s">
         <v>908</v>
       </c>
-      <c r="E31" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F31" s="24" t="s">
+      <c r="E31" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="G31" s="26" t="s">
+      <c r="G31" s="24" t="s">
         <v>909</v>
       </c>
-      <c r="H31" s="27">
+      <c r="H31" s="25">
         <v>220260</v>
       </c>
-      <c r="I31" s="29">
+      <c r="I31" s="32">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="J31" s="21">
+      <c r="J31" s="20">
         <f>I31*H31</f>
         <v>8369.8799999999992</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="19" t="s">
+      <c r="A32" s="18" t="s">
         <v>907</v>
       </c>
-      <c r="B32" s="21"/>
+      <c r="B32" s="20"/>
       <c r="C32" s="17"/>
-      <c r="D32" s="21" t="s">
+      <c r="D32" s="20" t="s">
         <v>908</v>
       </c>
-      <c r="E32" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="25" t="s">
+      <c r="E32" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="G32" s="21" t="s">
+      <c r="G32" s="20" t="s">
         <v>912</v>
       </c>
-      <c r="H32" s="27">
+      <c r="H32" s="25">
         <v>154070</v>
       </c>
-      <c r="I32" s="29">
+      <c r="I32" s="32">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="J32" s="21">
+      <c r="J32" s="20">
         <f>I32*H32</f>
         <v>3235.4700000000003</v>
       </c>
@@ -4380,7 +4388,7 @@
       <c r="H33" s="9">
         <v>209330</v>
       </c>
-      <c r="I33" s="8">
+      <c r="I33" s="31">
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="J33" s="8">
@@ -4412,7 +4420,7 @@
       <c r="H34" s="9">
         <v>204350</v>
       </c>
-      <c r="I34" s="8">
+      <c r="I34" s="31">
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="J34" s="8">
@@ -4444,7 +4452,7 @@
       <c r="H35" s="9">
         <v>220260</v>
       </c>
-      <c r="I35" s="8">
+      <c r="I35" s="31">
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="J35" s="8">
@@ -4476,7 +4484,7 @@
       <c r="H36" s="9">
         <v>108690</v>
       </c>
-      <c r="I36" s="8">
+      <c r="I36" s="31">
         <v>3.6999999999999998E-2</v>
       </c>
       <c r="J36" s="8">
@@ -4508,7 +4516,7 @@
       <c r="H37" s="9">
         <v>670520</v>
       </c>
-      <c r="I37" s="8">
+      <c r="I37" s="31">
         <v>3.1E-2</v>
       </c>
       <c r="J37" s="8">
@@ -4540,7 +4548,7 @@
       <c r="H38" s="9">
         <v>35580</v>
       </c>
-      <c r="I38" s="8">
+      <c r="I38" s="31">
         <v>0.06</v>
       </c>
       <c r="J38" s="8">
@@ -4572,7 +4580,7 @@
       <c r="H39" s="9">
         <v>17310</v>
       </c>
-      <c r="I39" s="8">
+      <c r="I39" s="31">
         <v>-2.1999999999999999E-2</v>
       </c>
       <c r="J39" s="8">
@@ -4604,7 +4612,7 @@
       <c r="H40" s="9">
         <v>53380</v>
       </c>
-      <c r="I40" s="8">
+      <c r="I40" s="31">
         <v>-2.8000000000000001E-2</v>
       </c>
       <c r="J40" s="8">
@@ -4636,7 +4644,7 @@
       <c r="H41" s="9">
         <v>670520</v>
       </c>
-      <c r="I41" s="8">
+      <c r="I41" s="31">
         <v>3.1E-2</v>
       </c>
       <c r="J41" s="8">
@@ -4668,7 +4676,7 @@
       <c r="H42" s="9">
         <v>114430</v>
       </c>
-      <c r="I42" s="8">
+      <c r="I42" s="31">
         <v>-7.0000000000000001E-3</v>
       </c>
       <c r="J42" s="8">
@@ -4700,7 +4708,7 @@
       <c r="H43" s="9">
         <v>53380</v>
       </c>
-      <c r="I43" s="8">
+      <c r="I43" s="31">
         <v>-2.8000000000000001E-2</v>
       </c>
       <c r="J43" s="8">
@@ -4732,7 +4740,7 @@
       <c r="H44" s="9">
         <v>89390</v>
       </c>
-      <c r="I44" s="8">
+      <c r="I44" s="31">
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="J44" s="8">
@@ -4764,7 +4772,7 @@
       <c r="H45" s="9">
         <v>13500</v>
       </c>
-      <c r="I45" s="8">
+      <c r="I45" s="31">
         <v>0.03</v>
       </c>
       <c r="J45" s="8">
@@ -4796,7 +4804,7 @@
       <c r="H46" s="9">
         <v>114430</v>
       </c>
-      <c r="I46" s="8">
+      <c r="I46" s="31">
         <v>-7.0000000000000001E-3</v>
       </c>
       <c r="J46" s="8">
@@ -4828,7 +4836,7 @@
       <c r="H47" s="9">
         <v>227760</v>
       </c>
-      <c r="I47" s="8">
+      <c r="I47" s="31">
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="J47" s="8">
@@ -4860,7 +4868,7 @@
       <c r="H48" s="9">
         <v>620090</v>
       </c>
-      <c r="I48" s="8">
+      <c r="I48" s="31">
         <v>-0.02</v>
       </c>
       <c r="J48" s="8">
@@ -4892,7 +4900,7 @@
       <c r="H49" s="9">
         <v>1065210</v>
       </c>
-      <c r="I49" s="8">
+      <c r="I49" s="31">
         <v>-1.6E-2</v>
       </c>
       <c r="J49" s="8">
@@ -4924,7 +4932,7 @@
       <c r="H50" s="9">
         <v>1388390</v>
       </c>
-      <c r="I50" s="8">
+      <c r="I50" s="31">
         <v>-0.02</v>
       </c>
       <c r="J50" s="8">
@@ -4956,7 +4964,7 @@
       <c r="H51" s="9">
         <v>190650</v>
       </c>
-      <c r="I51" s="8">
+      <c r="I51" s="31">
         <v>0.28499999999999998</v>
       </c>
       <c r="J51" s="8">
@@ -4988,7 +4996,7 @@
       <c r="H52" s="9">
         <v>435370</v>
       </c>
-      <c r="I52" s="8">
+      <c r="I52" s="31">
         <v>8.2000000000000003E-2</v>
       </c>
       <c r="J52" s="8">
@@ -5020,7 +5028,7 @@
       <c r="H53" s="9">
         <v>670570</v>
       </c>
-      <c r="I53" s="8">
+      <c r="I53" s="31">
         <v>0.152</v>
       </c>
       <c r="J53" s="8">
@@ -5052,7 +5060,7 @@
       <c r="H54" s="9">
         <v>190650</v>
       </c>
-      <c r="I54" s="8">
+      <c r="I54" s="31">
         <v>0.28499999999999998</v>
       </c>
       <c r="J54" s="8">
@@ -5084,7 +5092,7 @@
       <c r="H55" s="9">
         <v>114430</v>
       </c>
-      <c r="I55" s="8">
+      <c r="I55" s="31">
         <v>-7.0000000000000001E-3</v>
       </c>
       <c r="J55" s="8">
@@ -5114,7 +5122,7 @@
       <c r="H56" s="9">
         <v>262440</v>
       </c>
-      <c r="I56" s="8">
+      <c r="I56" s="31">
         <v>0.33500000000000002</v>
       </c>
       <c r="J56" s="8">
@@ -5144,7 +5152,7 @@
       <c r="H57" s="9">
         <v>26670</v>
       </c>
-      <c r="I57" s="8">
+      <c r="I57" s="31">
         <v>0.218</v>
       </c>
       <c r="J57" s="8">
@@ -5176,7 +5184,7 @@
       <c r="H58" s="9">
         <v>262440</v>
       </c>
-      <c r="I58" s="8">
+      <c r="I58" s="31">
         <v>0.33500000000000002</v>
       </c>
       <c r="J58" s="8">
@@ -5208,7 +5216,7 @@
       <c r="H59" s="9">
         <v>899580</v>
       </c>
-      <c r="I59" s="8">
+      <c r="I59" s="31">
         <v>6.7000000000000004E-2</v>
       </c>
       <c r="J59" s="8">
@@ -5240,7 +5248,7 @@
       <c r="H60" s="9">
         <v>395240</v>
       </c>
-      <c r="I60" s="8">
+      <c r="I60" s="31">
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="J60" s="8">
@@ -5270,7 +5278,7 @@
       <c r="H61" s="9">
         <v>262440</v>
       </c>
-      <c r="I61" s="8">
+      <c r="I61" s="31">
         <v>0.33500000000000002</v>
       </c>
       <c r="J61" s="8">
@@ -5300,7 +5308,7 @@
       <c r="H62" s="9">
         <v>67140</v>
       </c>
-      <c r="I62" s="8">
+      <c r="I62" s="31">
         <v>8.6999999999999994E-2</v>
       </c>
       <c r="J62" s="8">
@@ -5330,7 +5338,7 @@
       <c r="H63" s="9">
         <v>29030</v>
       </c>
-      <c r="I63" s="8">
+      <c r="I63" s="31">
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="J63" s="8">
@@ -5362,7 +5370,7 @@
       <c r="H64" s="9">
         <v>143120</v>
       </c>
-      <c r="I64" s="8">
+      <c r="I64" s="31">
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="J64" s="8">
@@ -5394,7 +5402,7 @@
       <c r="H65" s="9">
         <v>91690</v>
       </c>
-      <c r="I65" s="8">
+      <c r="I65" s="31">
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="J65" s="8">
@@ -5426,7 +5434,7 @@
       <c r="H66" s="9">
         <v>39250</v>
       </c>
-      <c r="I66" s="8">
+      <c r="I66" s="31">
         <v>-3.9E-2</v>
       </c>
       <c r="J66" s="8">
@@ -5458,7 +5466,7 @@
       <c r="H67" s="9">
         <v>113330</v>
       </c>
-      <c r="I67" s="8">
+      <c r="I67" s="31">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="J67" s="8">
@@ -5490,7 +5498,7 @@
       <c r="H68" s="9">
         <v>197830</v>
       </c>
-      <c r="I68" s="8">
+      <c r="I68" s="31">
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="J68" s="8">
@@ -5522,7 +5530,7 @@
       <c r="H69" s="9">
         <v>53070</v>
       </c>
-      <c r="I69" s="8">
+      <c r="I69" s="31">
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="J69" s="8">
@@ -5554,7 +5562,7 @@
       <c r="H70" s="9">
         <v>19970</v>
       </c>
-      <c r="I70" s="8">
+      <c r="I70" s="31">
         <v>1.6E-2</v>
       </c>
       <c r="J70" s="8">
@@ -5586,7 +5594,7 @@
       <c r="H71" s="9">
         <v>899580</v>
       </c>
-      <c r="I71" s="8">
+      <c r="I71" s="31">
         <v>6.7000000000000004E-2</v>
       </c>
       <c r="J71" s="8">
@@ -5618,7 +5626,7 @@
       <c r="H72" s="9">
         <v>17790</v>
       </c>
-      <c r="I72" s="8">
+      <c r="I72" s="31">
         <v>1.2E-2</v>
       </c>
       <c r="J72" s="8">
@@ -5650,7 +5658,7 @@
       <c r="H73" s="9">
         <v>899580</v>
       </c>
-      <c r="I73" s="8">
+      <c r="I73" s="31">
         <v>6.7000000000000004E-2</v>
       </c>
       <c r="J73" s="8">
@@ -5682,7 +5690,7 @@
       <c r="H74" s="9">
         <v>17790</v>
       </c>
-      <c r="I74" s="8">
+      <c r="I74" s="31">
         <v>1.2E-2</v>
       </c>
       <c r="J74" s="8">
@@ -5714,7 +5722,7 @@
       <c r="H75" s="9">
         <v>89250</v>
       </c>
-      <c r="I75" s="8">
+      <c r="I75" s="31">
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="J75" s="8">
@@ -5746,7 +5754,7 @@
       <c r="H76" s="9">
         <v>25950</v>
       </c>
-      <c r="I76" s="8">
+      <c r="I76" s="31">
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="J76" s="8">
@@ -5776,7 +5784,7 @@
       <c r="H77" s="9">
         <v>353310</v>
       </c>
-      <c r="I77" s="8">
+      <c r="I77" s="31">
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="J77" s="8">
@@ -5806,7 +5814,7 @@
       <c r="H78" s="9">
         <v>180470</v>
       </c>
-      <c r="I78" s="8">
+      <c r="I78" s="31">
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="J78" s="8">
@@ -5836,7 +5844,7 @@
       <c r="H79" s="9">
         <v>227760</v>
       </c>
-      <c r="I79" s="8">
+      <c r="I79" s="31">
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="J79" s="8">
@@ -5866,7 +5874,7 @@
       <c r="H80" s="9">
         <v>55130</v>
       </c>
-      <c r="I80" s="8">
+      <c r="I80" s="31">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="J80" s="8">
@@ -5896,7 +5904,7 @@
       <c r="H81" s="9">
         <v>60830</v>
       </c>
-      <c r="I81" s="8">
+      <c r="I81" s="31">
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="J81" s="8">
@@ -5926,7 +5934,7 @@
       <c r="H82" s="9">
         <v>328330</v>
       </c>
-      <c r="I82" s="8">
+      <c r="I82" s="31">
         <v>-1.4999999999999999E-2</v>
       </c>
       <c r="J82" s="8">
@@ -5958,7 +5966,7 @@
       <c r="H83" s="9">
         <v>180470</v>
       </c>
-      <c r="I83" s="8">
+      <c r="I83" s="31">
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="J83" s="8">
@@ -5990,7 +5998,7 @@
       <c r="H84" s="9">
         <v>73660</v>
       </c>
-      <c r="I84" s="8">
+      <c r="I84" s="31">
         <v>-2.5000000000000001E-2</v>
       </c>
       <c r="J84" s="8">
@@ -6022,7 +6030,7 @@
       <c r="H85" s="9">
         <v>328330</v>
       </c>
-      <c r="I85" s="8">
+      <c r="I85" s="31">
         <v>-1.4999999999999999E-2</v>
       </c>
       <c r="J85" s="8">
@@ -6054,7 +6062,7 @@
       <c r="H86" s="9">
         <v>198750</v>
       </c>
-      <c r="I86" s="8">
+      <c r="I86" s="31">
         <v>7.1999999999999995E-2</v>
       </c>
       <c r="J86" s="8">
@@ -6086,7 +6094,7 @@
       <c r="H87" s="9">
         <v>220260</v>
       </c>
-      <c r="I87" s="8">
+      <c r="I87" s="31">
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="J87" s="8">
@@ -6118,7 +6126,7 @@
       <c r="H88" s="9">
         <v>417070</v>
       </c>
-      <c r="I88" s="8">
+      <c r="I88" s="31">
         <v>0.03</v>
       </c>
       <c r="J88" s="8">
@@ -6150,7 +6158,7 @@
       <c r="H89" s="9">
         <v>89250</v>
       </c>
-      <c r="I89" s="8">
+      <c r="I89" s="31">
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="J89" s="8">
@@ -6182,7 +6190,7 @@
       <c r="H90" s="9">
         <v>25950</v>
       </c>
-      <c r="I90" s="8">
+      <c r="I90" s="31">
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="J90" s="8">
@@ -6214,7 +6222,7 @@
       <c r="H91" s="9">
         <v>417070</v>
       </c>
-      <c r="I91" s="8">
+      <c r="I91" s="31">
         <v>0.03</v>
       </c>
       <c r="J91" s="8">
@@ -6246,7 +6254,7 @@
       <c r="H92" s="9">
         <v>89250</v>
       </c>
-      <c r="I92" s="8">
+      <c r="I92" s="31">
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="J92" s="8">
@@ -6278,7 +6286,7 @@
       <c r="H93" s="9">
         <v>25950</v>
       </c>
-      <c r="I93" s="8">
+      <c r="I93" s="31">
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="J93" s="8">
@@ -6310,7 +6318,7 @@
       <c r="H94" s="9">
         <v>220260</v>
       </c>
-      <c r="I94" s="8">
+      <c r="I94" s="31">
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="J94" s="8">
@@ -6342,7 +6350,7 @@
       <c r="H95" s="9">
         <v>154070</v>
       </c>
-      <c r="I95" s="8">
+      <c r="I95" s="31">
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="J95" s="8">
@@ -6374,7 +6382,7 @@
       <c r="H96" s="9">
         <v>220260</v>
       </c>
-      <c r="I96" s="8">
+      <c r="I96" s="31">
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="J96" s="8">
@@ -6404,7 +6412,7 @@
       <c r="H97" s="9">
         <v>670570</v>
       </c>
-      <c r="I97" s="8">
+      <c r="I97" s="31">
         <v>0.152</v>
       </c>
       <c r="J97" s="8">
@@ -6434,7 +6442,7 @@
       <c r="H98" s="9">
         <v>519530</v>
       </c>
-      <c r="I98" s="8">
+      <c r="I98" s="31">
         <v>8.6999999999999994E-2</v>
       </c>
       <c r="J98" s="8">
@@ -6464,7 +6472,7 @@
       <c r="H99" s="9">
         <v>67140</v>
       </c>
-      <c r="I99" s="8">
+      <c r="I99" s="31">
         <v>8.6999999999999994E-2</v>
       </c>
       <c r="J99" s="8">
@@ -6494,7 +6502,7 @@
       <c r="H100" s="9">
         <v>519530</v>
       </c>
-      <c r="I100" s="8">
+      <c r="I100" s="31">
         <v>8.6999999999999994E-2</v>
       </c>
       <c r="J100" s="8">
@@ -6524,7 +6532,7 @@
       <c r="H101" s="9">
         <v>67140</v>
       </c>
-      <c r="I101" s="8">
+      <c r="I101" s="31">
         <v>8.6999999999999994E-2</v>
       </c>
       <c r="J101" s="8">
@@ -6554,7 +6562,7 @@
       <c r="H102" s="9">
         <v>69990</v>
       </c>
-      <c r="I102" s="8">
+      <c r="I102" s="31">
         <v>-7.0000000000000001E-3</v>
       </c>
       <c r="J102" s="8">
@@ -6586,7 +6594,7 @@
       <c r="H103" s="9">
         <v>841710</v>
       </c>
-      <c r="I103" s="8">
+      <c r="I103" s="31">
         <v>0.14799999999999999</v>
       </c>
       <c r="J103" s="8">
@@ -6618,7 +6626,7 @@
       <c r="H104" s="9">
         <v>361980</v>
       </c>
-      <c r="I104" s="8">
+      <c r="I104" s="31">
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="J104" s="8">
@@ -6650,7 +6658,7 @@
       <c r="H105" s="9">
         <v>47160</v>
       </c>
-      <c r="I105" s="8">
+      <c r="I105" s="31">
         <v>0.01</v>
       </c>
       <c r="J105" s="8">
@@ -6682,7 +6690,7 @@
       <c r="H106" s="9">
         <v>64390</v>
       </c>
-      <c r="I106" s="8">
+      <c r="I106" s="31">
         <v>-4.3999999999999997E-2</v>
       </c>
       <c r="J106" s="8">
@@ -6714,7 +6722,7 @@
       <c r="H107" s="9">
         <v>841710</v>
       </c>
-      <c r="I107" s="8">
+      <c r="I107" s="31">
         <v>0.14799999999999999</v>
       </c>
       <c r="J107" s="8">
@@ -6746,7 +6754,7 @@
       <c r="H108" s="9">
         <v>361980</v>
       </c>
-      <c r="I108" s="8">
+      <c r="I108" s="31">
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="J108" s="8">
@@ -6778,7 +6786,7 @@
       <c r="H109" s="9">
         <v>204350</v>
       </c>
-      <c r="I109" s="8">
+      <c r="I109" s="31">
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="J109" s="8">
@@ -6810,7 +6818,7 @@
       <c r="H110" s="9">
         <v>262440</v>
       </c>
-      <c r="I110" s="8">
+      <c r="I110" s="31">
         <v>0.33500000000000002</v>
       </c>
       <c r="J110" s="8">
@@ -6842,7 +6850,7 @@
       <c r="H111" s="9">
         <v>898280</v>
       </c>
-      <c r="I111" s="8">
+      <c r="I111" s="31">
         <v>8.7999999999999995E-2</v>
       </c>
       <c r="J111" s="8">
@@ -6874,7 +6882,7 @@
       <c r="H112" s="9">
         <v>899580</v>
       </c>
-      <c r="I112" s="8">
+      <c r="I112" s="31">
         <v>6.7000000000000004E-2</v>
       </c>
       <c r="J112" s="8">
@@ -6906,7 +6914,7 @@
       <c r="H113" s="9">
         <v>361980</v>
       </c>
-      <c r="I113" s="8">
+      <c r="I113" s="31">
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="J113" s="8">
@@ -6938,7 +6946,7 @@
       <c r="H114" s="9">
         <v>29030</v>
       </c>
-      <c r="I114" s="8">
+      <c r="I114" s="31">
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="J114" s="8">
@@ -6970,7 +6978,7 @@
       <c r="H115" s="9">
         <v>47160</v>
       </c>
-      <c r="I115" s="8">
+      <c r="I115" s="31">
         <v>0.01</v>
       </c>
       <c r="J115" s="8">
@@ -7002,7 +7010,7 @@
       <c r="H116" s="9">
         <v>4710</v>
       </c>
-      <c r="I116" s="8">
+      <c r="I116" s="31">
         <v>-2.5000000000000001E-2</v>
       </c>
       <c r="J116" s="8">
@@ -7034,7 +7042,7 @@
       <c r="H117" s="9">
         <v>64390</v>
       </c>
-      <c r="I117" s="8">
+      <c r="I117" s="31">
         <v>-4.3999999999999997E-2</v>
       </c>
       <c r="J117" s="8">
@@ -7066,7 +7074,7 @@
       <c r="H118" s="9">
         <v>106770</v>
       </c>
-      <c r="I118" s="8">
+      <c r="I118" s="31">
         <v>3.9E-2</v>
       </c>
       <c r="J118" s="8">
@@ -7098,7 +7106,7 @@
       <c r="H119" s="9">
         <v>44230</v>
       </c>
-      <c r="I119" s="8">
+      <c r="I119" s="31">
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="J119" s="8">
@@ -7130,7 +7138,7 @@
       <c r="H120" s="9">
         <v>58010</v>
       </c>
-      <c r="I120" s="8">
+      <c r="I120" s="31">
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="J120" s="8">
@@ -7162,7 +7170,7 @@
       <c r="H121" s="9">
         <v>14260</v>
       </c>
-      <c r="I121" s="8">
+      <c r="I121" s="31">
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="J121" s="8">
@@ -7194,7 +7202,7 @@
       <c r="H122" s="9">
         <v>22300</v>
       </c>
-      <c r="I122" s="8">
+      <c r="I122" s="31">
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="J122" s="8">
@@ -7226,7 +7234,7 @@
       <c r="H123" s="9">
         <v>1400</v>
       </c>
-      <c r="I123" s="8">
+      <c r="I123" s="31">
         <v>-3.1E-2</v>
       </c>
       <c r="J123" s="8">
@@ -7258,7 +7266,7 @@
       <c r="H124" s="9">
         <v>597080</v>
       </c>
-      <c r="I124" s="8">
+      <c r="I124" s="31">
         <v>0.23200000000000001</v>
       </c>
       <c r="J124" s="8">
@@ -7290,7 +7298,7 @@
       <c r="H125" s="9">
         <v>597080</v>
       </c>
-      <c r="I125" s="8">
+      <c r="I125" s="31">
         <v>0.23200000000000001</v>
       </c>
       <c r="J125" s="8">
@@ -7322,7 +7330,7 @@
       <c r="H126" s="9">
         <v>180470</v>
       </c>
-      <c r="I126" s="8">
+      <c r="I126" s="31">
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="J126" s="8">
@@ -7354,7 +7362,7 @@
       <c r="H127" s="9">
         <v>53500</v>
       </c>
-      <c r="I127" s="8">
+      <c r="I127" s="31">
         <v>8.1000000000000003E-2</v>
       </c>
       <c r="J127" s="8">
@@ -7386,7 +7394,7 @@
       <c r="H128" s="9">
         <v>3450</v>
       </c>
-      <c r="I128" s="8">
+      <c r="I128" s="31">
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="J128" s="8">
@@ -7418,7 +7426,7 @@
       <c r="H129" s="9">
         <v>13500</v>
       </c>
-      <c r="I129" s="8">
+      <c r="I129" s="31">
         <v>0.03</v>
       </c>
       <c r="J129" s="8">
@@ -7450,7 +7458,7 @@
       <c r="H130" s="9">
         <v>114430</v>
       </c>
-      <c r="I130" s="8">
+      <c r="I130" s="31">
         <v>-7.0000000000000001E-3</v>
       </c>
       <c r="J130" s="8">
@@ -7482,7 +7490,7 @@
       <c r="H131" s="9">
         <v>190650</v>
       </c>
-      <c r="I131" s="8">
+      <c r="I131" s="31">
         <v>0.28499999999999998</v>
       </c>
       <c r="J131" s="8">
@@ -7514,7 +7522,7 @@
       <c r="H132" s="9">
         <v>179740</v>
       </c>
-      <c r="I132" s="8">
+      <c r="I132" s="31">
         <v>0.11899999999999999</v>
       </c>
       <c r="J132" s="8">
@@ -7546,7 +7554,7 @@
       <c r="H133" s="9">
         <v>114430</v>
       </c>
-      <c r="I133" s="8">
+      <c r="I133" s="31">
         <v>-7.0000000000000001E-3</v>
       </c>
       <c r="J133" s="8">
@@ -7578,7 +7586,7 @@
       <c r="H134" s="9">
         <v>190650</v>
       </c>
-      <c r="I134" s="8">
+      <c r="I134" s="31">
         <v>0.28499999999999998</v>
       </c>
       <c r="J134" s="8">
@@ -7610,7 +7618,7 @@
       <c r="H135" s="9">
         <v>19120</v>
       </c>
-      <c r="I135" s="8">
+      <c r="I135" s="31">
         <v>0.128</v>
       </c>
       <c r="J135" s="8">
@@ -7642,7 +7650,7 @@
       <c r="H136" s="9">
         <v>114430</v>
       </c>
-      <c r="I136" s="8">
+      <c r="I136" s="31">
         <v>-7.0000000000000001E-3</v>
       </c>
       <c r="J136" s="8">
@@ -7674,7 +7682,7 @@
       <c r="H137" s="9">
         <v>435370</v>
       </c>
-      <c r="I137" s="8">
+      <c r="I137" s="31">
         <v>8.2000000000000003E-2</v>
       </c>
       <c r="J137" s="8">
@@ -7706,7 +7714,7 @@
       <c r="H138" s="9">
         <v>114430</v>
       </c>
-      <c r="I138" s="8">
+      <c r="I138" s="31">
         <v>-7.0000000000000001E-3</v>
       </c>
       <c r="J138" s="8">
@@ -7738,7 +7746,7 @@
       <c r="H139" s="9">
         <v>597080</v>
       </c>
-      <c r="I139" s="8">
+      <c r="I139" s="31">
         <v>0.23200000000000001</v>
       </c>
       <c r="J139" s="8">
@@ -7770,7 +7778,7 @@
       <c r="H140" s="9">
         <v>13500</v>
       </c>
-      <c r="I140" s="8">
+      <c r="I140" s="31">
         <v>0.03</v>
       </c>
       <c r="J140" s="8">
@@ -7802,7 +7810,7 @@
       <c r="H141" s="9">
         <v>13500</v>
       </c>
-      <c r="I141" s="8">
+      <c r="I141" s="31">
         <v>0.03</v>
       </c>
       <c r="J141" s="8">
@@ -7834,7 +7842,7 @@
       <c r="H142" s="9">
         <v>437860</v>
       </c>
-      <c r="I142" s="8">
+      <c r="I142" s="31">
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="J142" s="8">
@@ -7866,7 +7874,7 @@
       <c r="H143" s="9">
         <v>478780</v>
       </c>
-      <c r="I143" s="8">
+      <c r="I143" s="31">
         <v>4.1000000000000002E-2</v>
       </c>
       <c r="J143" s="8">
@@ -7898,7 +7906,7 @@
       <c r="H144" s="9">
         <v>1420350</v>
       </c>
-      <c r="I144" s="8">
+      <c r="I144" s="31">
         <v>-1.4999999999999999E-2</v>
       </c>
       <c r="J144" s="8">
@@ -7930,7 +7938,7 @@
       <c r="H145" s="9">
         <v>437860</v>
       </c>
-      <c r="I145" s="8">
+      <c r="I145" s="31">
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="J145" s="8">
@@ -7962,7 +7970,7 @@
       <c r="H146" s="9">
         <v>478780</v>
       </c>
-      <c r="I146" s="8">
+      <c r="I146" s="31">
         <v>4.1000000000000002E-2</v>
       </c>
       <c r="J146" s="8">
@@ -7994,7 +8002,7 @@
       <c r="H147" s="9">
         <v>392550</v>
       </c>
-      <c r="I147" s="8">
+      <c r="I147" s="31">
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="J147" s="8">
@@ -8024,7 +8032,7 @@
       <c r="H148" s="9">
         <v>220660</v>
       </c>
-      <c r="I148" s="8">
+      <c r="I148" s="31">
         <v>0.05</v>
       </c>
       <c r="J148" s="8">
@@ -8054,7 +8062,7 @@
       <c r="H149" s="9">
         <v>48050</v>
       </c>
-      <c r="I149" s="8">
+      <c r="I149" s="31">
         <v>5.8000000000000003E-2</v>
       </c>
       <c r="J149" s="8">
@@ -8084,7 +8092,7 @@
       <c r="H150" s="9">
         <v>22940</v>
       </c>
-      <c r="I150" s="8">
+      <c r="I150" s="31">
         <v>2E-3</v>
       </c>
       <c r="J150" s="8">
@@ -8116,7 +8124,7 @@
       <c r="H151" s="9">
         <v>365740</v>
       </c>
-      <c r="I151" s="8">
+      <c r="I151" s="31">
         <v>0.11</v>
       </c>
       <c r="J151" s="8">
@@ -8148,7 +8156,7 @@
       <c r="H152" s="9">
         <v>220260</v>
       </c>
-      <c r="I152" s="8">
+      <c r="I152" s="31">
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="J152" s="8">
@@ -8180,7 +8188,7 @@
       <c r="H153" s="9">
         <v>246250</v>
       </c>
-      <c r="I153" s="8">
+      <c r="I153" s="31">
         <v>1.9E-2</v>
       </c>
       <c r="J153" s="8">
@@ -8212,7 +8220,7 @@
       <c r="H154" s="9">
         <v>670570</v>
       </c>
-      <c r="I154" s="8">
+      <c r="I154" s="31">
         <v>0.152</v>
       </c>
       <c r="J154" s="8">
@@ -8244,7 +8252,7 @@
       <c r="H155" s="9">
         <v>519530</v>
       </c>
-      <c r="I155" s="8">
+      <c r="I155" s="31">
         <v>8.6999999999999994E-2</v>
       </c>
       <c r="J155" s="8">
@@ -8276,7 +8284,7 @@
       <c r="H156" s="9">
         <v>146190</v>
       </c>
-      <c r="I156" s="8">
+      <c r="I156" s="31">
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="J156" s="8">
@@ -8308,7 +8316,7 @@
       <c r="H157" s="9">
         <v>314340</v>
       </c>
-      <c r="I157" s="8">
+      <c r="I157" s="31">
         <v>-4.2000000000000003E-2</v>
       </c>
       <c r="J157" s="8">
@@ -8340,7 +8348,7 @@
       <c r="H158" s="9">
         <v>670570</v>
       </c>
-      <c r="I158" s="8">
+      <c r="I158" s="31">
         <v>0.152</v>
       </c>
       <c r="J158" s="8">
@@ -8372,7 +8380,7 @@
       <c r="H159" s="9">
         <v>67140</v>
       </c>
-      <c r="I159" s="8">
+      <c r="I159" s="31">
         <v>8.6999999999999994E-2</v>
       </c>
       <c r="J159" s="8">
@@ -8404,7 +8412,7 @@
       <c r="H160" s="9">
         <v>70190</v>
       </c>
-      <c r="I160" s="8">
+      <c r="I160" s="31">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="J160" s="8">
@@ -8436,7 +8444,7 @@
       <c r="H161" s="9">
         <v>69990</v>
       </c>
-      <c r="I161" s="8">
+      <c r="I161" s="31">
         <v>-7.0000000000000001E-3</v>
       </c>
       <c r="J161" s="8">
@@ -8468,7 +8476,7 @@
       <c r="H162" s="9">
         <v>92230</v>
       </c>
-      <c r="I162" s="8">
+      <c r="I162" s="31">
         <v>-0.06</v>
       </c>
       <c r="J162" s="8">
@@ -8500,7 +8508,7 @@
       <c r="H163" s="9">
         <v>314340</v>
       </c>
-      <c r="I163" s="8">
+      <c r="I163" s="31">
         <v>-4.2000000000000003E-2</v>
       </c>
       <c r="J163" s="8">
@@ -8532,7 +8540,7 @@
       <c r="H164" s="9">
         <v>912430</v>
       </c>
-      <c r="I164" s="8">
+      <c r="I164" s="31">
         <v>6.2E-2</v>
       </c>
       <c r="J164" s="8">
@@ -8564,7 +8572,7 @@
       <c r="H165" s="9">
         <v>64810</v>
       </c>
-      <c r="I165" s="8">
+      <c r="I165" s="31">
         <v>-1E-3</v>
       </c>
       <c r="J165" s="8">
@@ -8596,7 +8604,7 @@
       <c r="H166" s="9">
         <v>90220</v>
       </c>
-      <c r="I166" s="8">
+      <c r="I166" s="31">
         <v>-7.0999999999999994E-2</v>
       </c>
       <c r="J166" s="8">
@@ -8628,7 +8636,7 @@
       <c r="H167" s="9">
         <v>912430</v>
       </c>
-      <c r="I167" s="8">
+      <c r="I167" s="31">
         <v>6.2E-2</v>
       </c>
       <c r="J167" s="8">
@@ -8660,7 +8668,7 @@
       <c r="H168" s="9">
         <v>220660</v>
       </c>
-      <c r="I168" s="8">
+      <c r="I168" s="31">
         <v>0.05</v>
       </c>
       <c r="J168" s="8">
@@ -8692,7 +8700,7 @@
       <c r="H169" s="9">
         <v>9210</v>
       </c>
-      <c r="I169" s="8">
+      <c r="I169" s="31">
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="J169" s="8">
@@ -8724,7 +8732,7 @@
       <c r="H170" s="9">
         <v>22940</v>
       </c>
-      <c r="I170" s="8">
+      <c r="I170" s="31">
         <v>2E-3</v>
       </c>
       <c r="J170" s="8">
@@ -8756,7 +8764,7 @@
       <c r="H171" s="9">
         <v>64810</v>
       </c>
-      <c r="I171" s="8">
+      <c r="I171" s="31">
         <v>-1E-3</v>
       </c>
       <c r="J171" s="8">
@@ -8788,7 +8796,7 @@
       <c r="H172" s="9">
         <v>912430</v>
       </c>
-      <c r="I172" s="8">
+      <c r="I172" s="31">
         <v>6.2E-2</v>
       </c>
       <c r="J172" s="8">
@@ -8820,7 +8828,7 @@
       <c r="H173" s="9">
         <v>220660</v>
       </c>
-      <c r="I173" s="8">
+      <c r="I173" s="31">
         <v>0.05</v>
       </c>
       <c r="J173" s="8">
@@ -8852,7 +8860,7 @@
       <c r="H174" s="9">
         <v>9210</v>
       </c>
-      <c r="I174" s="8">
+      <c r="I174" s="31">
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="J174" s="8">
@@ -8884,7 +8892,7 @@
       <c r="H175" s="9">
         <v>22940</v>
       </c>
-      <c r="I175" s="8">
+      <c r="I175" s="31">
         <v>2E-3</v>
       </c>
       <c r="J175" s="8">
@@ -8916,7 +8924,7 @@
       <c r="H176" s="9">
         <v>64810</v>
       </c>
-      <c r="I176" s="8">
+      <c r="I176" s="31">
         <v>-1E-3</v>
       </c>
       <c r="J176" s="8">
@@ -8948,7 +8956,7 @@
       <c r="H177" s="9">
         <v>392880</v>
       </c>
-      <c r="I177" s="8">
+      <c r="I177" s="31">
         <v>2E-3</v>
       </c>
       <c r="J177" s="8">
@@ -8980,7 +8988,7 @@
       <c r="H178" s="9">
         <v>46760</v>
       </c>
-      <c r="I178" s="8">
+      <c r="I178" s="31">
         <v>-1.2E-2</v>
       </c>
       <c r="J178" s="8">
@@ -9012,7 +9020,7 @@
       <c r="H179" s="9">
         <v>458300</v>
       </c>
-      <c r="I179" s="8">
+      <c r="I179" s="31">
         <v>0.108</v>
       </c>
       <c r="J179" s="8">
@@ -9044,7 +9052,7 @@
       <c r="H180" s="9">
         <v>227760</v>
       </c>
-      <c r="I180" s="8">
+      <c r="I180" s="31">
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="J180" s="8">
@@ -9076,7 +9084,7 @@
       <c r="H181" s="9">
         <v>133790</v>
       </c>
-      <c r="I181" s="8">
+      <c r="I181" s="31">
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="J181" s="8">
@@ -9108,7 +9116,7 @@
       <c r="H182" s="9">
         <v>458300</v>
       </c>
-      <c r="I182" s="8">
+      <c r="I182" s="31">
         <v>0.108</v>
       </c>
       <c r="J182" s="8">
@@ -9140,7 +9148,7 @@
       <c r="H183" s="9">
         <v>37310</v>
       </c>
-      <c r="I183" s="8">
+      <c r="I183" s="31">
         <v>-0.13700000000000001</v>
       </c>
       <c r="J183" s="8">
@@ -9172,7 +9180,7 @@
       <c r="H184" s="9">
         <v>899580</v>
       </c>
-      <c r="I184" s="8">
+      <c r="I184" s="31">
         <v>6.7000000000000004E-2</v>
       </c>
       <c r="J184" s="8">
@@ -9204,7 +9212,7 @@
       <c r="H185" s="9">
         <v>395240</v>
       </c>
-      <c r="I185" s="8">
+      <c r="I185" s="31">
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="J185" s="8">
@@ -9236,7 +9244,7 @@
       <c r="H186" s="9">
         <v>21470</v>
       </c>
-      <c r="I186" s="8">
+      <c r="I186" s="31">
         <v>-2.1999999999999999E-2</v>
       </c>
       <c r="J186" s="8">
@@ -9268,7 +9276,7 @@
       <c r="H187" s="9">
         <v>899580</v>
       </c>
-      <c r="I187" s="8">
+      <c r="I187" s="31">
         <v>6.7000000000000004E-2</v>
       </c>
       <c r="J187" s="8">
@@ -9300,7 +9308,7 @@
       <c r="H188" s="9">
         <v>395240</v>
       </c>
-      <c r="I188" s="8">
+      <c r="I188" s="31">
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="J188" s="8">
@@ -9330,7 +9338,7 @@
       <c r="H189" s="9">
         <v>1687890</v>
       </c>
-      <c r="I189" s="8">
+      <c r="I189" s="31">
         <v>0.158</v>
       </c>
       <c r="J189" s="8">
@@ -9360,7 +9368,7 @@
       <c r="H190" s="9">
         <v>670570</v>
       </c>
-      <c r="I190" s="8">
+      <c r="I190" s="31">
         <v>0.152</v>
       </c>
       <c r="J190" s="8">
@@ -9390,7 +9398,7 @@
       <c r="H191" s="9">
         <v>262440</v>
       </c>
-      <c r="I191" s="8">
+      <c r="I191" s="31">
         <v>0.33500000000000002</v>
       </c>
       <c r="J191" s="8">
@@ -9420,7 +9428,7 @@
       <c r="H192" s="9">
         <v>190650</v>
       </c>
-      <c r="I192" s="8">
+      <c r="I192" s="31">
         <v>0.28499999999999998</v>
       </c>
       <c r="J192" s="8">
@@ -9450,7 +9458,7 @@
       <c r="H193" s="9">
         <v>519530</v>
       </c>
-      <c r="I193" s="8">
+      <c r="I193" s="31">
         <v>8.6999999999999994E-2</v>
       </c>
       <c r="J193" s="8">
@@ -9480,7 +9488,7 @@
       <c r="H194" s="9">
         <v>179740</v>
       </c>
-      <c r="I194" s="8">
+      <c r="I194" s="31">
         <v>0.11899999999999999</v>
       </c>
       <c r="J194" s="8">
@@ -9510,7 +9518,7 @@
       <c r="H195" s="9">
         <v>67140</v>
       </c>
-      <c r="I195" s="8">
+      <c r="I195" s="31">
         <v>8.6999999999999994E-2</v>
       </c>
       <c r="J195" s="8">
@@ -9540,7 +9548,7 @@
       <c r="H196" s="9">
         <v>69990</v>
       </c>
-      <c r="I196" s="8">
+      <c r="I196" s="31">
         <v>-7.0000000000000001E-3</v>
       </c>
       <c r="J196" s="8">
@@ -9570,7 +9578,7 @@
       <c r="H197" s="9">
         <v>670570</v>
       </c>
-      <c r="I197" s="8">
+      <c r="I197" s="31">
         <v>0.152</v>
       </c>
       <c r="J197" s="8">
@@ -9600,7 +9608,7 @@
       <c r="H198" s="9">
         <v>262440</v>
       </c>
-      <c r="I198" s="8">
+      <c r="I198" s="31">
         <v>0.33500000000000002</v>
       </c>
       <c r="J198" s="8">
@@ -9630,7 +9638,7 @@
       <c r="H199" s="9">
         <v>519530</v>
       </c>
-      <c r="I199" s="8">
+      <c r="I199" s="31">
         <v>8.6999999999999994E-2</v>
       </c>
       <c r="J199" s="8">
@@ -9660,7 +9668,7 @@
       <c r="H200" s="9">
         <v>67140</v>
       </c>
-      <c r="I200" s="8">
+      <c r="I200" s="31">
         <v>8.6999999999999994E-2</v>
       </c>
       <c r="J200" s="8">
@@ -9690,7 +9698,7 @@
       <c r="H201" s="9">
         <v>69990</v>
       </c>
-      <c r="I201" s="8">
+      <c r="I201" s="31">
         <v>-7.0000000000000001E-3</v>
       </c>
       <c r="J201" s="8">
@@ -9722,7 +9730,7 @@
       <c r="H202" s="9">
         <v>296810</v>
       </c>
-      <c r="I202" s="8">
+      <c r="I202" s="31">
         <v>9.0999999999999998E-2</v>
       </c>
       <c r="J202" s="8">
@@ -9754,7 +9762,7 @@
       <c r="H203" s="9">
         <v>220260</v>
       </c>
-      <c r="I203" s="8">
+      <c r="I203" s="31">
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="J203" s="8">
@@ -9786,7 +9794,7 @@
       <c r="H204" s="9">
         <v>220260</v>
       </c>
-      <c r="I204" s="8">
+      <c r="I204" s="31">
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="J204" s="8">
@@ -9818,7 +9826,7 @@
       <c r="H205" s="9">
         <v>15280</v>
       </c>
-      <c r="I205" s="8">
+      <c r="I205" s="31">
         <v>-1.0999999999999999E-2</v>
       </c>
       <c r="J205" s="8">
@@ -9848,7 +9856,7 @@
       <c r="H206" s="9">
         <v>220260</v>
       </c>
-      <c r="I206" s="8">
+      <c r="I206" s="31">
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="J206" s="8">
@@ -9878,7 +9886,7 @@
       <c r="H207" s="9">
         <v>15280</v>
       </c>
-      <c r="I207" s="8">
+      <c r="I207" s="31">
         <v>-1.0999999999999999E-2</v>
       </c>
       <c r="J207" s="8">
@@ -9910,7 +9918,7 @@
       <c r="H208" s="9">
         <v>3379720</v>
       </c>
-      <c r="I208" s="8">
+      <c r="I208" s="31">
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="J208" s="8">
@@ -9942,7 +9950,7 @@
       <c r="H209" s="9">
         <v>597080</v>
       </c>
-      <c r="I209" s="8">
+      <c r="I209" s="31">
         <v>0.23200000000000001</v>
       </c>
       <c r="J209" s="8">
@@ -9974,7 +9982,7 @@
       <c r="H210" s="9">
         <v>77960</v>
       </c>
-      <c r="I210" s="8">
+      <c r="I210" s="31">
         <v>0.16800000000000001</v>
       </c>
       <c r="J210" s="8">
@@ -10006,7 +10014,7 @@
       <c r="H211" s="9">
         <v>3379720</v>
       </c>
-      <c r="I211" s="8">
+      <c r="I211" s="31">
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="J211" s="8">
@@ -10038,7 +10046,7 @@
       <c r="H212" s="9">
         <v>597080</v>
       </c>
-      <c r="I212" s="8">
+      <c r="I212" s="31">
         <v>0.23200000000000001</v>
       </c>
       <c r="J212" s="8">
@@ -10070,7 +10078,7 @@
       <c r="H213" s="9">
         <v>323040</v>
       </c>
-      <c r="I213" s="8">
+      <c r="I213" s="31">
         <v>0.40100000000000002</v>
       </c>
       <c r="J213" s="8">
@@ -10102,7 +10110,7 @@
       <c r="H214" s="9">
         <v>77960</v>
       </c>
-      <c r="I214" s="8">
+      <c r="I214" s="31">
         <v>0.16800000000000001</v>
       </c>
       <c r="J214" s="8">
@@ -10134,7 +10142,7 @@
       <c r="H215" s="9">
         <v>597080</v>
       </c>
-      <c r="I215" s="8">
+      <c r="I215" s="31">
         <v>0.23200000000000001</v>
       </c>
       <c r="J215" s="8">
@@ -10166,7 +10174,7 @@
       <c r="H216" s="9">
         <v>323040</v>
       </c>
-      <c r="I216" s="8">
+      <c r="I216" s="31">
         <v>0.40100000000000002</v>
       </c>
       <c r="J216" s="8">
@@ -10198,7 +10206,7 @@
       <c r="H217" s="9">
         <v>77570</v>
       </c>
-      <c r="I217" s="8">
+      <c r="I217" s="31">
         <v>5.5E-2</v>
       </c>
       <c r="J217" s="8">
@@ -10230,7 +10238,7 @@
       <c r="H218" s="9">
         <v>48050</v>
       </c>
-      <c r="I218" s="8">
+      <c r="I218" s="31">
         <v>5.8000000000000003E-2</v>
       </c>
       <c r="J218" s="8">
@@ -10262,7 +10270,7 @@
       <c r="H219" s="9">
         <v>283380</v>
       </c>
-      <c r="I219" s="8">
+      <c r="I219" s="31">
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="J219" s="8">
@@ -10294,7 +10302,7 @@
       <c r="H220" s="9">
         <v>111040</v>
       </c>
-      <c r="I220" s="8">
+      <c r="I220" s="31">
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="J220" s="8">
@@ -10326,7 +10334,7 @@
       <c r="H221" s="9">
         <v>47940</v>
       </c>
-      <c r="I221" s="8">
+      <c r="I221" s="31">
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="J221" s="8">
@@ -10358,7 +10366,7 @@
       <c r="H222" s="9">
         <v>91690</v>
       </c>
-      <c r="I222" s="8">
+      <c r="I222" s="31">
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="J222" s="8">
@@ -10390,7 +10398,7 @@
       <c r="H223" s="9">
         <v>45500</v>
       </c>
-      <c r="I223" s="8">
+      <c r="I223" s="31">
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="J223" s="8">
@@ -10422,7 +10430,7 @@
       <c r="H224" s="9">
         <v>39250</v>
       </c>
-      <c r="I224" s="8">
+      <c r="I224" s="31">
         <v>-3.9E-2</v>
       </c>
       <c r="J224" s="8">
@@ -10454,7 +10462,7 @@
       <c r="H225" s="9">
         <v>283380</v>
       </c>
-      <c r="I225" s="8">
+      <c r="I225" s="31">
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="J225" s="8">
@@ -10486,7 +10494,7 @@
       <c r="H226" s="9">
         <v>111040</v>
       </c>
-      <c r="I226" s="8">
+      <c r="I226" s="31">
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="J226" s="8">
@@ -10518,7 +10526,7 @@
       <c r="H227" s="9">
         <v>47940</v>
       </c>
-      <c r="I227" s="8">
+      <c r="I227" s="31">
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="J227" s="8">
@@ -10550,7 +10558,7 @@
       <c r="H228" s="9">
         <v>91690</v>
       </c>
-      <c r="I228" s="8">
+      <c r="I228" s="31">
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="J228" s="8">
@@ -10582,7 +10590,7 @@
       <c r="H229" s="9">
         <v>45500</v>
       </c>
-      <c r="I229" s="8">
+      <c r="I229" s="31">
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="J229" s="8">
@@ -10614,7 +10622,7 @@
       <c r="H230" s="9">
         <v>39250</v>
       </c>
-      <c r="I230" s="8">
+      <c r="I230" s="31">
         <v>-3.9E-2</v>
       </c>
       <c r="J230" s="8">
@@ -10646,7 +10654,7 @@
       <c r="H231" s="9">
         <v>3503020</v>
       </c>
-      <c r="I231" s="8">
+      <c r="I231" s="31">
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="J231" s="8">
@@ -10678,7 +10686,7 @@
       <c r="H232" s="9">
         <v>637080</v>
       </c>
-      <c r="I232" s="8">
+      <c r="I232" s="31">
         <v>4.7E-2</v>
       </c>
       <c r="J232" s="8">
@@ -10710,7 +10718,7 @@
       <c r="H233" s="9">
         <v>38810</v>
       </c>
-      <c r="I233" s="8">
+      <c r="I233" s="31">
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="J233" s="8">
@@ -10742,7 +10750,7 @@
       <c r="H234" s="9">
         <v>3503020</v>
       </c>
-      <c r="I234" s="8">
+      <c r="I234" s="31">
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="J234" s="8">
@@ -10774,7 +10782,7 @@
       <c r="H235" s="9">
         <v>637080</v>
       </c>
-      <c r="I235" s="8">
+      <c r="I235" s="31">
         <v>4.7E-2</v>
       </c>
       <c r="J235" s="8">
@@ -10806,7 +10814,7 @@
       <c r="H236" s="9">
         <v>38810</v>
       </c>
-      <c r="I236" s="8">
+      <c r="I236" s="31">
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="J236" s="8">
@@ -10838,7 +10846,7 @@
       <c r="H237" s="9">
         <v>30640</v>
       </c>
-      <c r="I237" s="8">
+      <c r="I237" s="31">
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="J237" s="8">
@@ -10870,7 +10878,7 @@
       <c r="H238" s="9">
         <v>5540</v>
       </c>
-      <c r="I238" s="8">
+      <c r="I238" s="31">
         <v>-3.1E-2</v>
       </c>
       <c r="J238" s="8">
@@ -10902,7 +10910,7 @@
       <c r="H239" s="9">
         <v>30640</v>
       </c>
-      <c r="I239" s="8">
+      <c r="I239" s="31">
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="J239" s="8">
@@ -10934,7 +10942,7 @@
       <c r="H240" s="9">
         <v>5540</v>
       </c>
-      <c r="I240" s="8">
+      <c r="I240" s="31">
         <v>-3.1E-2</v>
       </c>
       <c r="J240" s="8">
@@ -10966,7 +10974,7 @@
       <c r="H241" s="9">
         <v>1066670</v>
       </c>
-      <c r="I241" s="8">
+      <c r="I241" s="31">
         <v>5.6000000000000001E-2</v>
       </c>
       <c r="J241" s="8">
@@ -10998,7 +11006,7 @@
       <c r="H242" s="9">
         <v>251040</v>
       </c>
-      <c r="I242" s="8">
+      <c r="I242" s="31">
         <v>0.16700000000000001</v>
       </c>
       <c r="J242" s="8">
@@ -11030,7 +11038,7 @@
       <c r="H243" s="9">
         <v>221180</v>
       </c>
-      <c r="I243" s="8">
+      <c r="I243" s="31">
         <v>6.0999999999999999E-2</v>
       </c>
       <c r="J243" s="8">
@@ -11062,7 +11070,7 @@
       <c r="H244" s="9">
         <v>246250</v>
       </c>
-      <c r="I244" s="8">
+      <c r="I244" s="31">
         <v>1.9E-2</v>
       </c>
       <c r="J244" s="8">
@@ -11094,7 +11102,7 @@
       <c r="H245" s="9">
         <v>1066670</v>
       </c>
-      <c r="I245" s="8">
+      <c r="I245" s="31">
         <v>5.6000000000000001E-2</v>
       </c>
       <c r="J245" s="8">
@@ -11126,7 +11134,7 @@
       <c r="H246" s="9">
         <v>30640</v>
       </c>
-      <c r="I246" s="8">
+      <c r="I246" s="31">
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="J246" s="8">
@@ -11158,7 +11166,7 @@
       <c r="H247" s="9">
         <v>8290</v>
       </c>
-      <c r="I247" s="8">
+      <c r="I247" s="31">
         <v>-5.1999999999999998E-2</v>
       </c>
       <c r="J247" s="8">
@@ -11190,7 +11198,7 @@
       <c r="H248" s="9">
         <v>30640</v>
       </c>
-      <c r="I248" s="8">
+      <c r="I248" s="31">
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="J248" s="8">
@@ -11222,7 +11230,7 @@
       <c r="H249" s="9">
         <v>8290</v>
       </c>
-      <c r="I249" s="8">
+      <c r="I249" s="31">
         <v>-5.1999999999999998E-2</v>
       </c>
       <c r="J249" s="8">
@@ -11254,7 +11262,7 @@
       <c r="H250" s="9">
         <v>3503020</v>
       </c>
-      <c r="I250" s="8">
+      <c r="I250" s="31">
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="J250" s="8">
@@ -11286,7 +11294,7 @@
       <c r="H251" s="9">
         <v>209330</v>
       </c>
-      <c r="I251" s="8">
+      <c r="I251" s="31">
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="J251" s="8">
@@ -11318,7 +11326,7 @@
       <c r="H252" s="9">
         <v>74850</v>
       </c>
-      <c r="I252" s="8">
+      <c r="I252" s="31">
         <v>0.05</v>
       </c>
       <c r="J252" s="8">
@@ -11350,7 +11358,7 @@
       <c r="H253" s="9">
         <v>38810</v>
       </c>
-      <c r="I253" s="8">
+      <c r="I253" s="31">
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="J253" s="8">
@@ -11382,7 +11390,7 @@
       <c r="H254" s="9">
         <v>597080</v>
       </c>
-      <c r="I254" s="8">
+      <c r="I254" s="31">
         <v>0.23200000000000001</v>
       </c>
       <c r="J254" s="8">
@@ -11414,7 +11422,7 @@
       <c r="H255" s="9">
         <v>61660</v>
       </c>
-      <c r="I255" s="8">
+      <c r="I255" s="31">
         <v>0.113</v>
       </c>
       <c r="J255" s="8">
@@ -11446,7 +11454,7 @@
       <c r="H256" s="9">
         <v>65690</v>
       </c>
-      <c r="I256" s="8">
+      <c r="I256" s="31">
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="J256" s="8">
@@ -11476,7 +11484,7 @@
       <c r="H257" s="9">
         <v>331490</v>
       </c>
-      <c r="I257" s="8">
+      <c r="I257" s="31">
         <v>4.1000000000000002E-2</v>
       </c>
       <c r="J257" s="8">
@@ -11508,7 +11516,7 @@
       <c r="H258" s="9">
         <v>331490</v>
       </c>
-      <c r="I258" s="8">
+      <c r="I258" s="31">
         <v>4.1000000000000002E-2</v>
       </c>
       <c r="J258" s="8">
@@ -11540,7 +11548,7 @@
       <c r="H259" s="9">
         <v>108690</v>
       </c>
-      <c r="I259" s="8">
+      <c r="I259" s="31">
         <v>3.6999999999999998E-2</v>
       </c>
       <c r="J259" s="8">
@@ -11572,7 +11580,7 @@
       <c r="H260" s="9">
         <v>89250</v>
       </c>
-      <c r="I260" s="8">
+      <c r="I260" s="31">
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="J260" s="8">
@@ -11604,7 +11612,7 @@
       <c r="H261" s="9">
         <v>25950</v>
       </c>
-      <c r="I261" s="8">
+      <c r="I261" s="31">
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="J261" s="8">
@@ -11636,7 +11644,7 @@
       <c r="H262" s="9">
         <v>190650</v>
       </c>
-      <c r="I262" s="8">
+      <c r="I262" s="31">
         <v>0.28499999999999998</v>
       </c>
       <c r="J262" s="8">
@@ -11668,7 +11676,7 @@
       <c r="H263" s="9">
         <v>519530</v>
       </c>
-      <c r="I263" s="8">
+      <c r="I263" s="31">
         <v>8.6999999999999994E-2</v>
       </c>
       <c r="J263" s="8">
@@ -11700,7 +11708,7 @@
       <c r="H264" s="9">
         <v>314340</v>
       </c>
-      <c r="I264" s="8">
+      <c r="I264" s="31">
         <v>-4.2000000000000003E-2</v>
       </c>
       <c r="J264" s="8">
@@ -11730,7 +11738,7 @@
       <c r="H265" s="9">
         <v>187630</v>
       </c>
-      <c r="I265" s="8">
+      <c r="I265" s="31">
         <v>7.6999999999999999E-2</v>
       </c>
       <c r="J265" s="8">
@@ -11760,7 +11768,7 @@
       <c r="H266" s="9">
         <v>209330</v>
       </c>
-      <c r="I266" s="8">
+      <c r="I266" s="31">
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="J266" s="8">
@@ -11790,7 +11798,7 @@
       <c r="H267" s="9">
         <v>392550</v>
       </c>
-      <c r="I267" s="8">
+      <c r="I267" s="31">
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="J267" s="8">
@@ -11820,7 +11828,7 @@
       <c r="H268" s="9">
         <v>132810</v>
       </c>
-      <c r="I268" s="8">
+      <c r="I268" s="31">
         <v>9.7000000000000003E-2</v>
       </c>
       <c r="J268" s="8">
@@ -11850,7 +11858,7 @@
       <c r="H269" s="9">
         <v>28580</v>
       </c>
-      <c r="I269" s="8">
+      <c r="I269" s="31">
         <v>0.126</v>
       </c>
       <c r="J269" s="8">
@@ -11880,7 +11888,7 @@
       <c r="H270" s="9">
         <v>62930</v>
       </c>
-      <c r="I270" s="8">
+      <c r="I270" s="31">
         <v>3.9E-2</v>
       </c>
       <c r="J270" s="8">
@@ -11912,7 +11920,7 @@
       <c r="H271" s="9">
         <v>1687890</v>
       </c>
-      <c r="I271" s="8">
+      <c r="I271" s="31">
         <v>0.158</v>
       </c>
       <c r="J271" s="8">
@@ -11944,7 +11952,7 @@
       <c r="H272" s="9">
         <v>186740</v>
       </c>
-      <c r="I272" s="8">
+      <c r="I272" s="31">
         <v>0.1</v>
       </c>
       <c r="J272" s="8">
@@ -11976,7 +11984,7 @@
       <c r="H273" s="9">
         <v>1687890</v>
       </c>
-      <c r="I273" s="8">
+      <c r="I273" s="31">
         <v>0.158</v>
       </c>
       <c r="J273" s="8">
@@ -12008,7 +12016,7 @@
       <c r="H274" s="9">
         <v>670570</v>
       </c>
-      <c r="I274" s="8">
+      <c r="I274" s="31">
         <v>0.152</v>
       </c>
       <c r="J274" s="8">
@@ -12040,7 +12048,7 @@
       <c r="H275" s="9">
         <v>186740</v>
       </c>
-      <c r="I275" s="8">
+      <c r="I275" s="31">
         <v>0.1</v>
       </c>
       <c r="J275" s="8">
@@ -12072,7 +12080,7 @@
       <c r="H276" s="9">
         <v>262440</v>
       </c>
-      <c r="I276" s="8">
+      <c r="I276" s="31">
         <v>0.33500000000000002</v>
       </c>
       <c r="J276" s="8">
@@ -12104,7 +12112,7 @@
       <c r="H277" s="9">
         <v>58010</v>
       </c>
-      <c r="I277" s="8">
+      <c r="I277" s="31">
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="J277" s="8">
@@ -12136,7 +12144,7 @@
       <c r="H278" s="9">
         <v>14260</v>
       </c>
-      <c r="I278" s="8">
+      <c r="I278" s="31">
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="J278" s="8">
@@ -12168,7 +12176,7 @@
       <c r="H279" s="9">
         <v>22300</v>
       </c>
-      <c r="I279" s="8">
+      <c r="I279" s="31">
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="J279" s="8">
@@ -12200,7 +12208,7 @@
       <c r="H280" s="9">
         <v>1400</v>
       </c>
-      <c r="I280" s="8">
+      <c r="I280" s="31">
         <v>-3.1E-2</v>
       </c>
       <c r="J280" s="8">
@@ -12232,7 +12240,7 @@
       <c r="H281" s="9">
         <v>29510</v>
       </c>
-      <c r="I281" s="8">
+      <c r="I281" s="31">
         <v>1.4E-2</v>
       </c>
       <c r="J281" s="8">
@@ -12264,7 +12272,7 @@
       <c r="H282" s="9">
         <v>95200</v>
       </c>
-      <c r="I282" s="8">
+      <c r="I282" s="31">
         <v>-1.9E-2</v>
       </c>
       <c r="J282" s="8">
@@ -12296,7 +12304,7 @@
       <c r="H283" s="9">
         <v>163930</v>
       </c>
-      <c r="I283" s="8">
+      <c r="I283" s="31">
         <v>-1.6E-2</v>
       </c>
       <c r="J283" s="8">
@@ -12328,7 +12336,7 @@
       <c r="H284" s="9">
         <v>260870</v>
       </c>
-      <c r="I284" s="8">
+      <c r="I284" s="31">
         <v>-1.7999999999999999E-2</v>
       </c>
       <c r="J284" s="8">
@@ -12360,7 +12368,7 @@
       <c r="H285" s="9">
         <v>283380</v>
       </c>
-      <c r="I285" s="8">
+      <c r="I285" s="31">
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="J285" s="8">
@@ -12392,7 +12400,7 @@
       <c r="H286" s="9">
         <v>74850</v>
       </c>
-      <c r="I286" s="8">
+      <c r="I286" s="31">
         <v>0.05</v>
       </c>
       <c r="J286" s="8">
@@ -12424,7 +12432,7 @@
       <c r="H287" s="9">
         <v>21470</v>
       </c>
-      <c r="I287" s="8">
+      <c r="I287" s="31">
         <v>-2.1999999999999999E-2</v>
       </c>
       <c r="J287" s="8">
@@ -12456,7 +12464,7 @@
       <c r="H288" s="9">
         <v>74850</v>
       </c>
-      <c r="I288" s="8">
+      <c r="I288" s="31">
         <v>0.05</v>
       </c>
       <c r="J288" s="8">
@@ -12488,7 +12496,7 @@
       <c r="H289" s="9">
         <v>21470</v>
       </c>
-      <c r="I289" s="8">
+      <c r="I289" s="31">
         <v>-2.1999999999999999E-2</v>
       </c>
       <c r="J289" s="8">
@@ -12520,7 +12528,7 @@
       <c r="H290" s="9">
         <v>3503020</v>
       </c>
-      <c r="I290" s="8">
+      <c r="I290" s="31">
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="J290" s="8">
@@ -12552,7 +12560,7 @@
       <c r="H291" s="9">
         <v>898280</v>
       </c>
-      <c r="I291" s="8">
+      <c r="I291" s="31">
         <v>8.7999999999999995E-2</v>
       </c>
       <c r="J291" s="8">
@@ -12584,7 +12592,7 @@
       <c r="H292" s="9">
         <v>204350</v>
       </c>
-      <c r="I292" s="8">
+      <c r="I292" s="31">
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="J292" s="8">
@@ -12616,7 +12624,7 @@
       <c r="H293" s="9">
         <v>251040</v>
       </c>
-      <c r="I293" s="8">
+      <c r="I293" s="31">
         <v>0.16700000000000001</v>
       </c>
       <c r="J293" s="8">
@@ -12648,7 +12656,7 @@
       <c r="H294" s="9">
         <v>221180</v>
       </c>
-      <c r="I294" s="8">
+      <c r="I294" s="31">
         <v>6.0999999999999999E-2</v>
       </c>
       <c r="J294" s="8">
@@ -12680,7 +12688,7 @@
       <c r="H295" s="9">
         <v>519530</v>
       </c>
-      <c r="I295" s="8">
+      <c r="I295" s="31">
         <v>8.6999999999999994E-2</v>
       </c>
       <c r="J295" s="8">
@@ -12712,7 +12720,7 @@
       <c r="H296" s="9">
         <v>365740</v>
       </c>
-      <c r="I296" s="8">
+      <c r="I296" s="31">
         <v>0.11</v>
       </c>
       <c r="J296" s="8">
@@ -12744,7 +12752,7 @@
       <c r="H297" s="9">
         <v>435370</v>
       </c>
-      <c r="I297" s="8">
+      <c r="I297" s="31">
         <v>8.2000000000000003E-2</v>
       </c>
       <c r="J297" s="8">
@@ -12776,7 +12784,7 @@
       <c r="H298" s="9">
         <v>186740</v>
       </c>
-      <c r="I298" s="8">
+      <c r="I298" s="31">
         <v>0.1</v>
       </c>
       <c r="J298" s="8">
@@ -12806,7 +12814,7 @@
       <c r="H299" s="9">
         <v>1449500</v>
       </c>
-      <c r="I299" s="8">
+      <c r="I299" s="31">
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="J299" s="8">
@@ -12836,7 +12844,7 @@
       <c r="H300" s="9">
         <v>56610</v>
       </c>
-      <c r="I300" s="8">
+      <c r="I300" s="31">
         <v>-1.7999999999999999E-2</v>
       </c>
       <c r="J300" s="8">
@@ -12868,7 +12876,7 @@
       <c r="H301" s="9">
         <v>15730</v>
       </c>
-      <c r="I301" s="8">
+      <c r="I301" s="31">
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="J301" s="8">
@@ -12900,7 +12908,7 @@
       <c r="H302" s="9">
         <v>15130</v>
       </c>
-      <c r="I302" s="8">
+      <c r="I302" s="31">
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="J302" s="8">
@@ -12932,7 +12940,7 @@
       <c r="H303" s="9">
         <v>14410</v>
       </c>
-      <c r="I303" s="8">
+      <c r="I303" s="31">
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="J303" s="8">
@@ -12964,7 +12972,7 @@
       <c r="H304" s="16">
         <v>130760</v>
       </c>
-      <c r="I304" s="15">
+      <c r="I304" s="33">
         <v>2.3E-2</v>
       </c>
       <c r="J304" s="15">
@@ -12972,98 +12980,98 @@
       </c>
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A305" s="20" t="s">
+      <c r="A305" s="19" t="s">
         <v>452</v>
       </c>
-      <c r="B305" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C305" s="22">
+      <c r="B305" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C305" s="12">
         <v>23</v>
       </c>
-      <c r="D305" s="20" t="s">
+      <c r="D305" s="19" t="s">
         <v>453</v>
       </c>
-      <c r="E305" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F305" s="20" t="s">
+      <c r="E305" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F305" s="19" t="s">
         <v>454</v>
       </c>
-      <c r="G305" s="20" t="s">
+      <c r="G305" s="19" t="s">
         <v>455</v>
       </c>
-      <c r="H305" s="28">
+      <c r="H305" s="26">
         <v>952640</v>
       </c>
-      <c r="I305" s="22">
+      <c r="I305" s="34">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="J305" s="22">
+      <c r="J305" s="12">
         <v>34295.040000000001</v>
       </c>
     </row>
     <row r="306" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A306" s="20" t="s">
+      <c r="A306" s="19" t="s">
         <v>452</v>
       </c>
-      <c r="B306" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C306" s="22">
+      <c r="B306" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C306" s="12">
         <v>23</v>
       </c>
-      <c r="D306" s="20" t="s">
+      <c r="D306" s="19" t="s">
         <v>453</v>
       </c>
-      <c r="E306" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F306" s="20" t="s">
+      <c r="E306" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F306" s="19" t="s">
         <v>450</v>
       </c>
-      <c r="G306" s="20" t="s">
+      <c r="G306" s="19" t="s">
         <v>451</v>
       </c>
-      <c r="H306" s="28">
+      <c r="H306" s="26">
         <v>130760</v>
       </c>
-      <c r="I306" s="22">
+      <c r="I306" s="34">
         <v>2.3E-2</v>
       </c>
-      <c r="J306" s="22">
+      <c r="J306" s="12">
         <v>3007.48</v>
       </c>
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A307" s="20" t="s">
+      <c r="A307" s="19" t="s">
         <v>452</v>
       </c>
-      <c r="B307" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C307" s="22">
+      <c r="B307" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C307" s="12">
         <v>23</v>
       </c>
-      <c r="D307" s="20" t="s">
+      <c r="D307" s="19" t="s">
         <v>453</v>
       </c>
-      <c r="E307" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F307" s="20" t="s">
+      <c r="E307" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F307" s="19" t="s">
         <v>456</v>
       </c>
-      <c r="G307" s="20" t="s">
+      <c r="G307" s="19" t="s">
         <v>457</v>
       </c>
-      <c r="H307" s="28">
+      <c r="H307" s="26">
         <v>27050</v>
       </c>
-      <c r="I307" s="22">
+      <c r="I307" s="34">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="J307" s="22">
+      <c r="J307" s="12">
         <v>1027.9000000000001</v>
       </c>
     </row>
@@ -14001,19 +14009,19 @@
       </c>
     </row>
     <row r="55" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="30" t="s">
+      <c r="A55" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="B55" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="C55" s="31">
+      <c r="B55" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55" s="28">
         <v>24</v>
       </c>
-      <c r="D55" s="30" t="s">
+      <c r="D55" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="E55" s="30" t="s">
+      <c r="E55" s="27" t="s">
         <v>482</v>
       </c>
     </row>
@@ -14021,12 +14029,10 @@
       <c r="A56" s="17" t="s">
         <v>907</v>
       </c>
-      <c r="B56" s="18"/>
-      <c r="C56" s="18"/>
-      <c r="D56" s="18" t="s">
+      <c r="D56" t="s">
         <v>908</v>
       </c>
-      <c r="E56" s="18" t="s">
+      <c r="E56" t="s">
         <v>913</v>
       </c>
     </row>
@@ -14034,12 +14040,10 @@
       <c r="A57" s="17" t="s">
         <v>907</v>
       </c>
-      <c r="B57" s="18"/>
-      <c r="C57" s="18"/>
-      <c r="D57" s="18" t="s">
+      <c r="D57" t="s">
         <v>908</v>
       </c>
-      <c r="E57" s="18" t="s">
+      <c r="E57" t="s">
         <v>514</v>
       </c>
     </row>
@@ -14047,12 +14051,10 @@
       <c r="A58" s="17" t="s">
         <v>907</v>
       </c>
-      <c r="B58" s="18"/>
-      <c r="C58" s="18"/>
-      <c r="D58" s="18" t="s">
+      <c r="D58" t="s">
         <v>908</v>
       </c>
-      <c r="E58" s="18" t="s">
+      <c r="E58" t="s">
         <v>914</v>
       </c>
     </row>
@@ -14060,12 +14062,10 @@
       <c r="A59" s="17" t="s">
         <v>907</v>
       </c>
-      <c r="B59" s="18"/>
-      <c r="C59" s="18"/>
-      <c r="D59" s="18" t="s">
+      <c r="D59" t="s">
         <v>908</v>
       </c>
-      <c r="E59" s="18" t="s">
+      <c r="E59" t="s">
         <v>915</v>
       </c>
     </row>
@@ -14073,12 +14073,10 @@
       <c r="A60" s="17" t="s">
         <v>907</v>
       </c>
-      <c r="B60" s="18"/>
-      <c r="C60" s="18"/>
-      <c r="D60" s="18" t="s">
+      <c r="D60" t="s">
         <v>908</v>
       </c>
-      <c r="E60" s="18" t="s">
+      <c r="E60" t="s">
         <v>916</v>
       </c>
     </row>
@@ -14086,12 +14084,10 @@
       <c r="A61" s="17" t="s">
         <v>907</v>
       </c>
-      <c r="B61" s="18"/>
-      <c r="C61" s="18"/>
-      <c r="D61" s="18" t="s">
+      <c r="D61" t="s">
         <v>908</v>
       </c>
-      <c r="E61" s="18" t="s">
+      <c r="E61" t="s">
         <v>917</v>
       </c>
     </row>
@@ -14099,12 +14095,10 @@
       <c r="A62" s="17" t="s">
         <v>907</v>
       </c>
-      <c r="B62" s="18"/>
-      <c r="C62" s="18"/>
-      <c r="D62" s="18" t="s">
+      <c r="D62" t="s">
         <v>908</v>
       </c>
-      <c r="E62" s="18" t="s">
+      <c r="E62" t="s">
         <v>918</v>
       </c>
     </row>
@@ -14112,29 +14106,27 @@
       <c r="A63" s="17" t="s">
         <v>907</v>
       </c>
-      <c r="B63" s="18"/>
-      <c r="C63" s="18"/>
-      <c r="D63" s="18" t="s">
+      <c r="D63" t="s">
         <v>908</v>
       </c>
-      <c r="E63" s="18" t="s">
+      <c r="E63" t="s">
         <v>724</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="32" t="s">
+      <c r="A64" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="B64" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="C64" s="33">
+      <c r="B64" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64" s="30">
         <v>58</v>
       </c>
-      <c r="D64" s="32" t="s">
+      <c r="D64" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="E64" s="32" t="s">
+      <c r="E64" s="29" t="s">
         <v>703</v>
       </c>
     </row>
